--- a/output/17_전송망설계팀_판매단가_안내.xlsx
+++ b/output/17_전송망설계팀_판매단가_안내.xlsx
@@ -8,11 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="판매단가_안내(초안)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구성별_판매단가" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="K코드별_판매단가" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'구성별_판매단가'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'K코드별_판매단가'!$A$1:$C$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>전송망설계팀에 보낼 이메일 본문 초안. '구성별_판매단가' 시트를 표로 첨부하거나 붙여넣으면 된다.</t>
+          <t>전송망설계팀에 보낼 이메일 본문 초안. 'K코드별_판매단가' 시트를 표로 첨부하거나 붙여넣으면 된다.</t>
         </is>
       </c>
     </row>
@@ -492,16 +492,8 @@
         <is>
           <t>안녕하세요, 전송망설계팀 담당자님,
 KT commerce 이돈현입니다.
-금번 8GHz/11GHz 대역 MW 장비(Ceragon) 구성별 판매단가를 안내드립니다. 구성 x SD 여부별 1개 링크(양쪽 사이트 합산) 기준 단가는 아래와 같습니다.
-  8GHz 2+0  |  Non_SD 37,423,292원  |  SD 50,140,174원
-  8GHz 4+0  |  Non_SD 58,543,407원  |  SD 69,278,112원
-  8GHz 6+0  |  Non_SD 79,482,218원  |  SD 88,157,449원
-  8GHz 8+0  |  Non_SD 96,177,850원  |  SD 109,193,010원
-  11GHz 2+0  |  Non_SD 37,423,292원  |  SD 50,139,024원
-  11GHz 4+0  |  Non_SD 58,541,107원  |  SD 69,275,811원
-  11GHz 6+0  |  Non_SD 79,478,768원  |  SD 88,153,998원
-  11GHz 8+0  |  Non_SD 96,173,250원  |  SD 109,188,410원
-위 단가는 당사 표준 마진 정책(장비군별 2~5%)을 반영해 산정하였습니다. 세부 품목 구성이나 산정 근거가 필요하시면 말씀해 주시면 상세 자료를 공유드리겠습니다.
+금번 8GHz/11GHz 대역 MW 장비(Ceragon) 품목별 판매단가를 K코드 단위로 정리해 첨부(K코드별_판매단가 시트)해 드립니다. 단가는 EA(단품) 기준입니다.
+위 단가는 당사 표준 마진 정책(장비군별 2~5%)을 반영해 산정하였습니다. 산정 근거가 필요하시면 말씀해 주시면 상세 자료를 공유드리겠습니다.
 검토 후 문의사항 있으시면 편하게 연락 주세요.
 감사합니다.
 KT commerce 이돈현 드림</t>
@@ -523,17 +515,29 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>대상 품목 선정 근거(내부용)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>15번의 '계약범위 추정' 패턴 매칭(272개, 추정 다수 포함) 대신, 06번 BoM_상세에서 8GHz/11GHz 구성에 실제로 등장하는 49개 K코드만 포함했다 - 실제 BoM 구성 여부가 더 확실한 근거.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>이 초안은 자동 생성된 것이니 보내시기 전에 실제 상황(호칭, 첨부 형식, 일정 등)에 맞게 다듬어서 사용하시기 바랍니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B5"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -544,183 +548,768 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>대역</t>
+          <t>K코드</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>구성</t>
+          <t>품명</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 판매단가(1개 링크)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>SD 판매단가(1개 링크)</t>
+          <t>판매단가(EA)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>8GHz</t>
+          <t>K9178621</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2+0</t>
+          <t>CER_IP10-OP-SM-CBL-LC-LC-DPLX 3M</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>37423292</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>50140174</v>
+        <v>14688</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>8GHz</t>
+          <t>K9178832</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>4+0</t>
+          <t>CER_WG-Flex-1.2m-8GHz</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>58543407</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>69278112</v>
+        <v>491844</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>8GHz</t>
+          <t>K9178833</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>6+0</t>
+          <t>CER_WG-Flex-1.2m-11GHz</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>79482218</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>88157449</v>
+        <v>491844</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>8GHz</t>
+          <t>K9183526</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>8+0</t>
+          <t>CER_IP-20_Glands_kit</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>96177850</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>109193010</v>
+        <v>26176</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>11GHz</t>
+          <t>K9183528</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2+0</t>
+          <t>CER_CBL-GND</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>37423292</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>50139024</v>
+        <v>10670</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>11GHz</t>
+          <t>K9183529</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>4+0</t>
+          <t>CER_IP-20C_DC_Conn</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>58541107</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>69275811</v>
+        <v>3326</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>11GHz</t>
+          <t>K9187804</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>6+0</t>
+          <t>CER_IP-20N-1RU/5-Slot-Base-IDU</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>79478768</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>88153998</v>
+        <v>467716</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>11GHz</t>
+          <t>K9187805</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>8+0</t>
+          <t>CER_IP-20N-2RU/10-Slot-Base-IDU</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>96173250</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>109188410</v>
+        <v>718036</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>K9187820</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-PDC-A48-dual_1RU</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>264854</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>K9187821</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-PDC-B48_2RU</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>206681</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>K9187823</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-Fans-tray-1RU-IDU</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>59706</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>K9187824</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-Fans-tray-2RU-IDU</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>74250</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>K9187825</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-Filter-tray-1RU-IDU</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>22963</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>K9187826</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-Filter-tray-2RU-IDU</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>38268</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>K9187827</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CER_CBL-PWR-DType/OE-40A-22m</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>51664</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>K9187830</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>CER_CBL-PWR-OE-OE-16A-2.2m</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>20667</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>K9197221</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20-RIC-D</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1464822</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>K9197224</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFU-D-HP-08</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>7485191</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>K9197225</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFU-D-HP-11</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>7485191</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>K9197227</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFU-D-HP-08-Non TX/2RX_SD</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>57296</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>K9197228</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFU-D-HP-11-Non TX/2RX_SD</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>57296</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>K9197229</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH08-xxxY-BccN-H</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1703194</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>K9197230</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH08-xxxY-BccN-L</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1703194</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>K9197231</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH11-xxxY-BccN-H</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1703194</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>K9197232</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH11-xxxY-BccN-L</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>1702044</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>K9197233</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH08-xxxY-BccN-H - SD</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>69427</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>K9197234</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH08-xxxY-BccN-L - SD</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>69427</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>K9197235</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH11-xxxY-BccN-H - SD</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>69427</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>K9197236</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH11-xxxY-BccN-L - SD</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>69427</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>K9197237</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-MOUNT-kit</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>179164</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>K9197241</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-Term-7-8</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>89187</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>K9197242</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-Term-11</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>89187</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>K9197243</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-U-Bend-7-8</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>165886</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>K9197244</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-U-Bend-11</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>165886</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>K9197245</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-LU-Bend-7-8</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>157516</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>K9197246</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>CER_FXDH-RM-LU-Bend-11</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>157516</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>K9197304</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>CER_1G SFP 1310nm 10km, SMF</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>27007</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>K9197306</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>CER_10G SFP+ SR 850nm 300m, MMF</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>44362</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>K9197309</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>CER_2.5G SFP  1310nm 2km, SMF</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>48225</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>K9206942</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>CER_IP-20 TCC-U</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2701838</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>K9206945</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>CER_SL-IDU-Radio-Port-Act</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>264415</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>K9213023</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_2+0_SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>7491044</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>K9213024</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_2+0_ Non SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>4588310</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>K9213025</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_4+0_SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4863056</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>K9213026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_4+0_Non SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3550012</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>K9213027</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_6+0_SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1826945</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>K9213028</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_6+0_Non SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2449121</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>K9213029</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_8+0_SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>326933</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>K9213030</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>CER_8GHz_11GHz_8+0_Non SD_Configuration SW Package</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>901776</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:C50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/17_전송망설계팀_판매단가_안내.xlsx
+++ b/output/17_전송망설계팀_판매단가_안내.xlsx
@@ -1324,7 +1324,7 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>213231</v>
+        <v>207020</v>
       </c>
     </row>
     <row r="39">
@@ -2464,7 +2464,7 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>3599613</v>
+        <v>3494770</v>
       </c>
     </row>
     <row r="96">
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>3599613</v>
+        <v>3494770</v>
       </c>
     </row>
     <row r="97">
@@ -2504,7 +2504,7 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>3599613</v>
+        <v>3494770</v>
       </c>
     </row>
     <row r="98">
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>3599613</v>
+        <v>3494770</v>
       </c>
     </row>
     <row r="99">
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>5066765</v>
+        <v>4919190</v>
       </c>
     </row>
     <row r="100">
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>5066765</v>
+        <v>4919190</v>
       </c>
     </row>
     <row r="101">
@@ -2584,7 +2584,7 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>5066765</v>
+        <v>4919190</v>
       </c>
     </row>
     <row r="102">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>5066765</v>
+        <v>4919190</v>
       </c>
     </row>
     <row r="103">
@@ -2624,7 +2624,7 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>6738620</v>
+        <v>6542350</v>
       </c>
     </row>
     <row r="104">
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>6738620</v>
+        <v>6542350</v>
       </c>
     </row>
     <row r="105">
@@ -2664,7 +2664,7 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>6738620</v>
+        <v>6542350</v>
       </c>
     </row>
     <row r="106">
@@ -2684,7 +2684,7 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>6738620</v>
+        <v>6542350</v>
       </c>
     </row>
     <row r="107">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>8890507</v>
+        <v>8631560</v>
       </c>
     </row>
     <row r="108">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>8890507</v>
+        <v>8631560</v>
       </c>
     </row>
     <row r="109">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>8890507</v>
+        <v>8631560</v>
       </c>
     </row>
     <row r="110">
@@ -2764,7 +2764,7 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>8890507</v>
+        <v>8631560</v>
       </c>
     </row>
     <row r="111">
@@ -2784,7 +2784,7 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>11254830</v>
+        <v>10927020</v>
       </c>
     </row>
     <row r="112">
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>11254830</v>
+        <v>10927020</v>
       </c>
     </row>
     <row r="113">
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>11254830</v>
+        <v>10927020</v>
       </c>
     </row>
     <row r="114">
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>11254830</v>
+        <v>10927020</v>
       </c>
     </row>
     <row r="115">
@@ -2864,7 +2864,7 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>14588024</v>
+        <v>14163130</v>
       </c>
     </row>
     <row r="116">
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>14588024</v>
+        <v>14163130</v>
       </c>
     </row>
     <row r="117">
@@ -2904,7 +2904,7 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>14588024</v>
+        <v>14163130</v>
       </c>
     </row>
     <row r="118">
@@ -2924,7 +2924,7 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>14588024</v>
+        <v>14163130</v>
       </c>
     </row>
     <row r="119">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>5503485</v>
+        <v>5343190</v>
       </c>
     </row>
     <row r="123">
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>5503485</v>
+        <v>5343190</v>
       </c>
     </row>
     <row r="124">
@@ -3044,7 +3044,7 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>5503485</v>
+        <v>5343190</v>
       </c>
     </row>
     <row r="125">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>3115111</v>
+        <v>3024380</v>
       </c>
     </row>
     <row r="167">
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>3115111</v>
+        <v>3024380</v>
       </c>
     </row>
     <row r="168">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>3115111</v>
+        <v>3024380</v>
       </c>
     </row>
     <row r="169">
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>5503485</v>
+        <v>5343190</v>
       </c>
     </row>
     <row r="170">
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="D297" s="3" t="n">
-        <v>5611193</v>
+        <v>5447760</v>
       </c>
     </row>
     <row r="298">
@@ -6524,7 +6524,7 @@
         </is>
       </c>
       <c r="D298" s="3" t="n">
-        <v>3785353</v>
+        <v>3675100</v>
       </c>
     </row>
     <row r="299">
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="D299" s="3" t="n">
-        <v>2207805</v>
+        <v>2143500</v>
       </c>
     </row>
     <row r="300">
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="D300" s="3" t="n">
-        <v>930100</v>
+        <v>903010</v>
       </c>
     </row>
     <row r="301">
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="D301" s="3" t="n">
-        <v>750571</v>
+        <v>728710</v>
       </c>
     </row>
     <row r="302">
@@ -6604,7 +6604,7 @@
         </is>
       </c>
       <c r="D302" s="3" t="n">
-        <v>12127663</v>
+        <v>11774430</v>
       </c>
     </row>
     <row r="303">
@@ -8864,7 +8864,7 @@
         </is>
       </c>
       <c r="D415" s="3" t="n">
-        <v>27007</v>
+        <v>26220</v>
       </c>
     </row>
     <row r="416">
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="D417" s="3" t="n">
-        <v>44362</v>
+        <v>43070</v>
       </c>
     </row>
     <row r="418">
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="D420" s="3" t="n">
-        <v>48225</v>
+        <v>46820</v>
       </c>
     </row>
     <row r="421">
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="D442" s="3" t="n">
-        <v>7402641</v>
+        <v>7187030</v>
       </c>
     </row>
     <row r="443">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="D443" s="3" t="n">
-        <v>9000253</v>
+        <v>8738110</v>
       </c>
     </row>
     <row r="444">
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="D444" s="3" t="n">
-        <v>14218964</v>
+        <v>13804820</v>
       </c>
     </row>
     <row r="445">
@@ -9464,7 +9464,7 @@
         </is>
       </c>
       <c r="D445" s="3" t="n">
-        <v>18162845</v>
+        <v>17633830</v>
       </c>
     </row>
     <row r="446">

--- a/output/17_전송망설계팀_판매단가_안내.xlsx
+++ b/output/17_전송망설계팀_판매단가_안내.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체493종_판매단가_제시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체493종_판매단가_제시'!$A$1:$D$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체493종_판매단가_제시'!$A$1:$E$494</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,6 +92,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -459,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -502,6 +505,7 @@
 KT commerce 이돈현입니다.
 금번 8GHz/11GHz 대역 MW 장비(Ceragon) 전체 493개 품목의 판매단가를 K코드 단위로 정리해 첨부(전체493종_판매단가_제시 시트)해 드립니다. 단가는 EA(단품) 기준입니다.
 위 단가는 당사 표준 마진 정책(장비군별 2~5%)을 반영해 산정하였습니다. 산정 근거가 필요하시면 말씀해 주시면 상세 자료를 공유드리겠습니다.
+다만 4개 품목(K9213027~030, 8/11GHz 6+0/8+0 구성 SW패키지)은 공급사 측 가격 구조를 확인 중이라 잠정치입니다 - 확인 완료 후 갱신된 단가로 다시 안내드리겠습니다.
 검토 후 문의사항 있으시면 편하게 연락 주세요.
 감사합니다.
 KT commerce 이돈현 드림</t>
@@ -535,17 +539,29 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>확인 중 4개 품목(내부용)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>K9213027~030(8/11GHz 6+0/8+0 SD·Non_SD SW패키지)는 SD가 Non_SD보다 싼 역전 현상이 있어 대성에 확인 요청 중(18번 파일). 이 4개만 '확인 중(잠정치)'로 표시하고 나머지 489개는 그대로 전달 - 근거가 이 4개에 국한돼 전체를 늦출 필요는 없다는 판단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>주의</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>이 초안은 자동 생성된 것이니 보내시기 전에 실제 상황(호칭, 첨부 형식, 일정 등)에 맞게 다듬어서 사용하시기 바랍니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -556,13 +572,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D494"/>
+  <dimension ref="A1:E494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -586,6 +603,11 @@
           <t>판매단가(EA)</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -606,6 +628,7 @@
       <c r="D2" s="3" t="n">
         <v>510332</v>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -626,6 +649,7 @@
       <c r="D3" s="3" t="n">
         <v>299159</v>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -646,6 +670,7 @@
       <c r="D4" s="3" t="n">
         <v>299159</v>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -666,6 +691,7 @@
       <c r="D5" s="3" t="n">
         <v>281558</v>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -686,6 +712,7 @@
       <c r="D6" s="3" t="n">
         <v>14688</v>
       </c>
+      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -706,6 +733,7 @@
       <c r="D7" s="3" t="n">
         <v>356409</v>
       </c>
+      <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -726,6 +754,7 @@
       <c r="D8" s="3" t="n">
         <v>263958</v>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -746,6 +775,7 @@
       <c r="D9" s="3" t="n">
         <v>249486</v>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -766,6 +796,7 @@
       <c r="D10" s="3" t="n">
         <v>398882</v>
       </c>
+      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -786,6 +817,7 @@
       <c r="D11" s="3" t="n">
         <v>398882</v>
       </c>
+      <c r="E11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -806,6 +838,7 @@
       <c r="D12" s="3" t="n">
         <v>375417</v>
       </c>
+      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -826,6 +859,7 @@
       <c r="D13" s="3" t="n">
         <v>346080</v>
       </c>
+      <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -846,6 +880,7 @@
       <c r="D14" s="3" t="n">
         <v>451675</v>
       </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -866,6 +901,7 @@
       <c r="D15" s="3" t="n">
         <v>451675</v>
       </c>
+      <c r="E15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -886,6 +922,7 @@
       <c r="D16" s="3" t="n">
         <v>428210</v>
       </c>
+      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -906,6 +943,7 @@
       <c r="D17" s="3" t="n">
         <v>398882</v>
       </c>
+      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -926,6 +964,7 @@
       <c r="D18" s="3" t="n">
         <v>627656</v>
       </c>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -946,6 +985,7 @@
       <c r="D19" s="3" t="n">
         <v>627656</v>
       </c>
+      <c r="E19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -966,6 +1006,7 @@
       <c r="D20" s="3" t="n">
         <v>586590</v>
       </c>
+      <c r="E20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -986,6 +1027,7 @@
       <c r="D21" s="3" t="n">
         <v>533797</v>
       </c>
+      <c r="E21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1006,6 +1048,7 @@
       <c r="D22" s="3" t="n">
         <v>395534</v>
       </c>
+      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1026,6 +1069,7 @@
       <c r="D23" s="3" t="n">
         <v>395534</v>
       </c>
+      <c r="E23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1046,6 +1090,7 @@
       <c r="D24" s="3" t="n">
         <v>395534</v>
       </c>
+      <c r="E24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1066,6 +1111,7 @@
       <c r="D25" s="3" t="n">
         <v>395534</v>
       </c>
+      <c r="E25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1086,6 +1132,7 @@
       <c r="D26" s="3" t="n">
         <v>46920</v>
       </c>
+      <c r="E26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1106,6 +1153,7 @@
       <c r="D27" s="3" t="n">
         <v>46920</v>
       </c>
+      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1126,6 +1174,7 @@
       <c r="D28" s="3" t="n">
         <v>41056</v>
       </c>
+      <c r="E28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1146,6 +1195,7 @@
       <c r="D29" s="3" t="n">
         <v>588271</v>
       </c>
+      <c r="E29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1166,6 +1216,7 @@
       <c r="D30" s="3" t="n">
         <v>58808</v>
       </c>
+      <c r="E30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1186,6 +1237,7 @@
       <c r="D31" s="3" t="n">
         <v>779066</v>
       </c>
+      <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1206,6 +1258,7 @@
       <c r="D32" s="3" t="n">
         <v>228101</v>
       </c>
+      <c r="E32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1226,6 +1279,7 @@
       <c r="D33" s="3" t="n">
         <v>228101</v>
       </c>
+      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1246,6 +1300,7 @@
       <c r="D34" s="3" t="n">
         <v>228101</v>
       </c>
+      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1266,6 +1321,7 @@
       <c r="D35" s="3" t="n">
         <v>228101</v>
       </c>
+      <c r="E35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1286,6 +1342,7 @@
       <c r="D36" s="3" t="n">
         <v>215325</v>
       </c>
+      <c r="E36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1306,6 +1363,7 @@
       <c r="D37" s="3" t="n">
         <v>215325</v>
       </c>
+      <c r="E37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1326,6 +1384,7 @@
       <c r="D38" s="3" t="n">
         <v>207020</v>
       </c>
+      <c r="E38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1346,6 +1405,7 @@
       <c r="D39" s="3" t="n">
         <v>187533</v>
       </c>
+      <c r="E39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1366,6 +1426,7 @@
       <c r="D40" s="3" t="n">
         <v>187533</v>
       </c>
+      <c r="E40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1386,6 +1447,7 @@
       <c r="D41" s="3" t="n">
         <v>187533</v>
       </c>
+      <c r="E41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1406,6 +1468,7 @@
       <c r="D42" s="3" t="n">
         <v>297007</v>
       </c>
+      <c r="E42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1426,6 +1489,7 @@
       <c r="D43" s="3" t="n">
         <v>297007</v>
       </c>
+      <c r="E43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1446,6 +1510,7 @@
       <c r="D44" s="3" t="n">
         <v>297007</v>
       </c>
+      <c r="E44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1466,6 +1531,7 @@
       <c r="D45" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1486,6 +1552,7 @@
       <c r="D46" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1506,6 +1573,7 @@
       <c r="D47" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1526,6 +1594,7 @@
       <c r="D48" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1546,6 +1615,7 @@
       <c r="D49" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1566,6 +1636,7 @@
       <c r="D50" s="3" t="n">
         <v>2723025</v>
       </c>
+      <c r="E50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1586,6 +1657,7 @@
       <c r="D51" s="3" t="n">
         <v>3107955</v>
       </c>
+      <c r="E51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1606,6 +1678,7 @@
       <c r="D52" s="3" t="n">
         <v>3107955</v>
       </c>
+      <c r="E52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1626,6 +1699,7 @@
       <c r="D53" s="3" t="n">
         <v>3043793</v>
       </c>
+      <c r="E53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1646,6 +1720,7 @@
       <c r="D54" s="3" t="n">
         <v>3043793</v>
       </c>
+      <c r="E54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1666,6 +1741,7 @@
       <c r="D55" s="3" t="n">
         <v>3043793</v>
       </c>
+      <c r="E55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1686,6 +1762,7 @@
       <c r="D56" s="3" t="n">
         <v>3371697</v>
       </c>
+      <c r="E56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1706,6 +1783,7 @@
       <c r="D57" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1726,6 +1804,7 @@
       <c r="D58" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1746,6 +1825,7 @@
       <c r="D59" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1766,6 +1846,7 @@
       <c r="D60" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1786,6 +1867,7 @@
       <c r="D61" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1806,6 +1888,7 @@
       <c r="D62" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1826,6 +1909,7 @@
       <c r="D63" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1846,6 +1930,7 @@
       <c r="D64" s="3" t="n">
         <v>684314</v>
       </c>
+      <c r="E64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1866,6 +1951,7 @@
       <c r="D65" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1886,6 +1972,7 @@
       <c r="D66" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1906,6 +1993,7 @@
       <c r="D67" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1926,6 +2014,7 @@
       <c r="D68" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1946,6 +2035,7 @@
       <c r="D69" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1966,6 +2056,7 @@
       <c r="D70" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -1986,6 +2077,7 @@
       <c r="D71" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2006,6 +2098,7 @@
       <c r="D72" s="3" t="n">
         <v>969440</v>
       </c>
+      <c r="E72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2026,6 +2119,7 @@
       <c r="D73" s="3" t="n">
         <v>172831</v>
       </c>
+      <c r="E73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2046,6 +2140,7 @@
       <c r="D74" s="3" t="n">
         <v>24227</v>
       </c>
+      <c r="E74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2066,6 +2161,7 @@
       <c r="D75" s="3" t="n">
         <v>24227</v>
       </c>
+      <c r="E75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2086,6 +2182,7 @@
       <c r="D76" s="3" t="n">
         <v>24227</v>
       </c>
+      <c r="E76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2106,6 +2203,7 @@
       <c r="D77" s="3" t="n">
         <v>78401</v>
       </c>
+      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2126,6 +2224,7 @@
       <c r="D78" s="3" t="n">
         <v>78401</v>
       </c>
+      <c r="E78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2146,6 +2245,7 @@
       <c r="D79" s="3" t="n">
         <v>78401</v>
       </c>
+      <c r="E79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2166,6 +2266,7 @@
       <c r="D80" s="3" t="n">
         <v>63220</v>
       </c>
+      <c r="E80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2186,6 +2287,7 @@
       <c r="D81" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2206,6 +2308,7 @@
       <c r="D82" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2226,6 +2329,7 @@
       <c r="D83" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2246,6 +2350,7 @@
       <c r="D84" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2266,6 +2371,7 @@
       <c r="D85" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2286,6 +2392,7 @@
       <c r="D86" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2306,6 +2413,7 @@
       <c r="D87" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2326,6 +2434,7 @@
       <c r="D88" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2346,6 +2455,7 @@
       <c r="D89" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2366,6 +2476,7 @@
       <c r="D90" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2386,6 +2497,7 @@
       <c r="D91" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2406,6 +2518,7 @@
       <c r="D92" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2426,6 +2539,7 @@
       <c r="D93" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2446,6 +2560,7 @@
       <c r="D94" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2466,6 +2581,7 @@
       <c r="D95" s="3" t="n">
         <v>3494770</v>
       </c>
+      <c r="E95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2486,6 +2602,7 @@
       <c r="D96" s="3" t="n">
         <v>3494770</v>
       </c>
+      <c r="E96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2506,6 +2623,7 @@
       <c r="D97" s="3" t="n">
         <v>3494770</v>
       </c>
+      <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2526,6 +2644,7 @@
       <c r="D98" s="3" t="n">
         <v>3494770</v>
       </c>
+      <c r="E98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2546,6 +2665,7 @@
       <c r="D99" s="3" t="n">
         <v>4919190</v>
       </c>
+      <c r="E99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2566,6 +2686,7 @@
       <c r="D100" s="3" t="n">
         <v>4919190</v>
       </c>
+      <c r="E100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2586,6 +2707,7 @@
       <c r="D101" s="3" t="n">
         <v>4919190</v>
       </c>
+      <c r="E101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2606,6 +2728,7 @@
       <c r="D102" s="3" t="n">
         <v>4919190</v>
       </c>
+      <c r="E102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2626,6 +2749,7 @@
       <c r="D103" s="3" t="n">
         <v>6542350</v>
       </c>
+      <c r="E103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2646,6 +2770,7 @@
       <c r="D104" s="3" t="n">
         <v>6542350</v>
       </c>
+      <c r="E104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2666,6 +2791,7 @@
       <c r="D105" s="3" t="n">
         <v>6542350</v>
       </c>
+      <c r="E105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2686,6 +2812,7 @@
       <c r="D106" s="3" t="n">
         <v>6542350</v>
       </c>
+      <c r="E106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2706,6 +2833,7 @@
       <c r="D107" s="3" t="n">
         <v>8631560</v>
       </c>
+      <c r="E107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2726,6 +2854,7 @@
       <c r="D108" s="3" t="n">
         <v>8631560</v>
       </c>
+      <c r="E108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2746,6 +2875,7 @@
       <c r="D109" s="3" t="n">
         <v>8631560</v>
       </c>
+      <c r="E109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2766,6 +2896,7 @@
       <c r="D110" s="3" t="n">
         <v>8631560</v>
       </c>
+      <c r="E110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2786,6 +2917,7 @@
       <c r="D111" s="3" t="n">
         <v>10927020</v>
       </c>
+      <c r="E111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2806,6 +2938,7 @@
       <c r="D112" s="3" t="n">
         <v>10927020</v>
       </c>
+      <c r="E112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2826,6 +2959,7 @@
       <c r="D113" s="3" t="n">
         <v>10927020</v>
       </c>
+      <c r="E113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2846,6 +2980,7 @@
       <c r="D114" s="3" t="n">
         <v>10927020</v>
       </c>
+      <c r="E114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2866,6 +3001,7 @@
       <c r="D115" s="3" t="n">
         <v>14163130</v>
       </c>
+      <c r="E115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2886,6 +3022,7 @@
       <c r="D116" s="3" t="n">
         <v>14163130</v>
       </c>
+      <c r="E116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -2906,6 +3043,7 @@
       <c r="D117" s="3" t="n">
         <v>14163130</v>
       </c>
+      <c r="E117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -2926,6 +3064,7 @@
       <c r="D118" s="3" t="n">
         <v>14163130</v>
       </c>
+      <c r="E118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -2946,6 +3085,7 @@
       <c r="D119" s="3" t="n">
         <v>23761213</v>
       </c>
+      <c r="E119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -2966,6 +3106,7 @@
       <c r="D120" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -2986,6 +3127,7 @@
       <c r="D121" s="3" t="n">
         <v>2970144</v>
       </c>
+      <c r="E121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3006,6 +3148,7 @@
       <c r="D122" s="3" t="n">
         <v>5343190</v>
       </c>
+      <c r="E122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3026,6 +3169,7 @@
       <c r="D123" s="3" t="n">
         <v>5343190</v>
       </c>
+      <c r="E123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3046,6 +3190,7 @@
       <c r="D124" s="3" t="n">
         <v>5343190</v>
       </c>
+      <c r="E124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3066,6 +3211,7 @@
       <c r="D125" s="3" t="n">
         <v>491844</v>
       </c>
+      <c r="E125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3086,6 +3232,7 @@
       <c r="D126" s="3" t="n">
         <v>491844</v>
       </c>
+      <c r="E126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3106,6 +3253,7 @@
       <c r="D127" s="3" t="n">
         <v>491844</v>
       </c>
+      <c r="E127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3126,6 +3274,7 @@
       <c r="D128" s="3" t="n">
         <v>288770</v>
       </c>
+      <c r="E128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3146,6 +3295,7 @@
       <c r="D129" s="3" t="n">
         <v>288770</v>
       </c>
+      <c r="E129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3166,6 +3316,7 @@
       <c r="D130" s="3" t="n">
         <v>288770</v>
       </c>
+      <c r="E130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3186,6 +3337,7 @@
       <c r="D131" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3206,6 +3358,7 @@
       <c r="D132" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3226,6 +3379,7 @@
       <c r="D133" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3246,6 +3400,7 @@
       <c r="D134" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3266,6 +3421,7 @@
       <c r="D135" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3286,6 +3442,7 @@
       <c r="D136" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3306,6 +3463,7 @@
       <c r="D137" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3326,6 +3484,7 @@
       <c r="D138" s="3" t="n">
         <v>1746438</v>
       </c>
+      <c r="E138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3346,6 +3505,7 @@
       <c r="D139" s="3" t="n">
         <v>201637</v>
       </c>
+      <c r="E139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3366,6 +3526,7 @@
       <c r="D140" s="3" t="n">
         <v>206699</v>
       </c>
+      <c r="E140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3386,6 +3547,7 @@
       <c r="D141" s="3" t="n">
         <v>206699</v>
       </c>
+      <c r="E141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3406,6 +3568,7 @@
       <c r="D142" s="3" t="n">
         <v>206699</v>
       </c>
+      <c r="E142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3426,6 +3589,7 @@
       <c r="D143" s="3" t="n">
         <v>206699</v>
       </c>
+      <c r="E143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3446,6 +3610,7 @@
       <c r="D144" s="3" t="n">
         <v>491844</v>
       </c>
+      <c r="E144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3466,6 +3631,7 @@
       <c r="D145" s="3" t="n">
         <v>491844</v>
       </c>
+      <c r="E145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3486,6 +3652,7 @@
       <c r="D146" s="3" t="n">
         <v>484291</v>
       </c>
+      <c r="E146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3506,6 +3673,7 @@
       <c r="D147" s="3" t="n">
         <v>110473</v>
       </c>
+      <c r="E147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3526,6 +3694,7 @@
       <c r="D148" s="3" t="n">
         <v>110473</v>
       </c>
+      <c r="E148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3546,6 +3715,7 @@
       <c r="D149" s="3" t="n">
         <v>110473</v>
       </c>
+      <c r="E149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3566,6 +3736,7 @@
       <c r="D150" s="3" t="n">
         <v>49171</v>
       </c>
+      <c r="E150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3586,6 +3757,7 @@
       <c r="D151" s="3" t="n">
         <v>49171</v>
       </c>
+      <c r="E151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -3606,6 +3778,7 @@
       <c r="D152" s="3" t="n">
         <v>49171</v>
       </c>
+      <c r="E152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -3626,6 +3799,7 @@
       <c r="D153" s="3" t="n">
         <v>108025</v>
       </c>
+      <c r="E153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3646,6 +3820,7 @@
       <c r="D154" s="3" t="n">
         <v>677185</v>
       </c>
+      <c r="E154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3666,6 +3841,7 @@
       <c r="D155" s="3" t="n">
         <v>677185</v>
       </c>
+      <c r="E155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3686,6 +3862,7 @@
       <c r="D156" s="3" t="n">
         <v>677185</v>
       </c>
+      <c r="E156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3706,6 +3883,7 @@
       <c r="D157" s="3" t="n">
         <v>727676</v>
       </c>
+      <c r="E157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3726,6 +3904,7 @@
       <c r="D158" s="3" t="n">
         <v>727676</v>
       </c>
+      <c r="E158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3746,6 +3925,7 @@
       <c r="D159" s="3" t="n">
         <v>727676</v>
       </c>
+      <c r="E159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -3766,6 +3946,7 @@
       <c r="D160" s="3" t="n">
         <v>727676</v>
       </c>
+      <c r="E160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3786,6 +3967,7 @@
       <c r="D161" s="3" t="n">
         <v>1410357</v>
       </c>
+      <c r="E161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -3806,6 +3988,7 @@
       <c r="D162" s="3" t="n">
         <v>1410357</v>
       </c>
+      <c r="E162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -3826,6 +4009,7 @@
       <c r="D163" s="3" t="n">
         <v>1410357</v>
       </c>
+      <c r="E163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -3846,6 +4030,7 @@
       <c r="D164" s="3" t="n">
         <v>1410357</v>
       </c>
+      <c r="E164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -3866,6 +4051,7 @@
       <c r="D165" s="3" t="n">
         <v>2739692</v>
       </c>
+      <c r="E165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -3886,6 +4072,7 @@
       <c r="D166" s="3" t="n">
         <v>3024380</v>
       </c>
+      <c r="E166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -3906,6 +4093,7 @@
       <c r="D167" s="3" t="n">
         <v>3024380</v>
       </c>
+      <c r="E167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -3926,6 +4114,7 @@
       <c r="D168" s="3" t="n">
         <v>3024380</v>
       </c>
+      <c r="E168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -3946,6 +4135,7 @@
       <c r="D169" s="3" t="n">
         <v>5343190</v>
       </c>
+      <c r="E169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -3966,6 +4156,7 @@
       <c r="D170" s="3" t="n">
         <v>7343</v>
       </c>
+      <c r="E170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -3986,6 +4177,7 @@
       <c r="D171" s="3" t="n">
         <v>29395</v>
       </c>
+      <c r="E171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4006,6 +4198,7 @@
       <c r="D172" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4026,6 +4219,7 @@
       <c r="D173" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4046,6 +4240,7 @@
       <c r="D174" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4066,6 +4261,7 @@
       <c r="D175" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4086,6 +4282,7 @@
       <c r="D176" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4106,6 +4303,7 @@
       <c r="D177" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4126,6 +4324,7 @@
       <c r="D178" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4146,6 +4345,7 @@
       <c r="D179" s="3" t="n">
         <v>11581111</v>
       </c>
+      <c r="E179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4166,6 +4366,7 @@
       <c r="D180" s="3" t="n">
         <v>106621</v>
       </c>
+      <c r="E180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -4186,6 +4387,7 @@
       <c r="D181" s="3" t="n">
         <v>835520</v>
       </c>
+      <c r="E181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -4206,6 +4408,7 @@
       <c r="D182" s="3" t="n">
         <v>1035827</v>
       </c>
+      <c r="E182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -4226,6 +4429,7 @@
       <c r="D183" s="3" t="n">
         <v>835520</v>
       </c>
+      <c r="E183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -4246,6 +4450,7 @@
       <c r="D184" s="3" t="n">
         <v>1035827</v>
       </c>
+      <c r="E184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -4266,6 +4471,7 @@
       <c r="D185" s="3" t="n">
         <v>102906</v>
       </c>
+      <c r="E185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -4286,6 +4492,7 @@
       <c r="D186" s="3" t="n">
         <v>102924</v>
       </c>
+      <c r="E186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -4306,6 +4513,7 @@
       <c r="D187" s="3" t="n">
         <v>56066</v>
       </c>
+      <c r="E187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -4326,6 +4534,7 @@
       <c r="D188" s="3" t="n">
         <v>397635</v>
       </c>
+      <c r="E188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -4346,6 +4555,7 @@
       <c r="D189" s="3" t="n">
         <v>113037</v>
       </c>
+      <c r="E189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -4366,6 +4576,7 @@
       <c r="D190" s="3" t="n">
         <v>118946</v>
       </c>
+      <c r="E190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -4386,6 +4597,7 @@
       <c r="D191" s="3" t="n">
         <v>217181</v>
       </c>
+      <c r="E191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -4406,6 +4618,7 @@
       <c r="D192" s="3" t="n">
         <v>26176</v>
       </c>
+      <c r="E192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -4426,6 +4639,7 @@
       <c r="D193" s="3" t="n">
         <v>10670</v>
       </c>
+      <c r="E193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -4446,6 +4660,7 @@
       <c r="D194" s="3" t="n">
         <v>3326</v>
       </c>
+      <c r="E194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -4466,6 +4681,7 @@
       <c r="D195" s="3" t="n">
         <v>52595</v>
       </c>
+      <c r="E195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -4486,6 +4702,7 @@
       <c r="D196" s="3" t="n">
         <v>47597</v>
       </c>
+      <c r="E196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -4506,6 +4723,7 @@
       <c r="D197" s="3" t="n">
         <v>641536</v>
       </c>
+      <c r="E197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -4526,6 +4744,7 @@
       <c r="D198" s="3" t="n">
         <v>454428</v>
       </c>
+      <c r="E198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -4546,6 +4765,7 @@
       <c r="D199" s="3" t="n">
         <v>230540</v>
       </c>
+      <c r="E199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -4566,6 +4786,7 @@
       <c r="D200" s="3" t="n">
         <v>162379</v>
       </c>
+      <c r="E200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -4586,6 +4807,7 @@
       <c r="D201" s="3" t="n">
         <v>149019</v>
       </c>
+      <c r="E201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -4606,6 +4828,7 @@
       <c r="D202" s="3" t="n">
         <v>149019</v>
       </c>
+      <c r="E202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -4626,6 +4849,7 @@
       <c r="D203" s="3" t="n">
         <v>132306</v>
       </c>
+      <c r="E203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -4646,6 +4870,7 @@
       <c r="D204" s="3" t="n">
         <v>193124</v>
       </c>
+      <c r="E204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -4666,6 +4891,7 @@
       <c r="D205" s="3" t="n">
         <v>483191</v>
       </c>
+      <c r="E205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -4686,6 +4912,7 @@
       <c r="D206" s="3" t="n">
         <v>573930</v>
       </c>
+      <c r="E206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -4706,6 +4933,7 @@
       <c r="D207" s="3" t="n">
         <v>633313</v>
       </c>
+      <c r="E207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -4726,6 +4954,7 @@
       <c r="D208" s="3" t="n">
         <v>2612516</v>
       </c>
+      <c r="E208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -4746,6 +4975,7 @@
       <c r="D209" s="3" t="n">
         <v>163571</v>
       </c>
+      <c r="E209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -4766,6 +4996,7 @@
       <c r="D210" s="3" t="n">
         <v>170171</v>
       </c>
+      <c r="E210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -4786,6 +5017,7 @@
       <c r="D211" s="3" t="n">
         <v>4754</v>
       </c>
+      <c r="E211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -4806,6 +5038,7 @@
       <c r="D212" s="3" t="n">
         <v>7899</v>
       </c>
+      <c r="E212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -4826,6 +5059,7 @@
       <c r="D213" s="3" t="n">
         <v>17000</v>
       </c>
+      <c r="E213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -4846,6 +5080,7 @@
       <c r="D214" s="3" t="n">
         <v>56057</v>
       </c>
+      <c r="E214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -4866,6 +5101,7 @@
       <c r="D215" s="3" t="n">
         <v>219900</v>
       </c>
+      <c r="E215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -4886,6 +5122,7 @@
       <c r="D216" s="3" t="n">
         <v>467716</v>
       </c>
+      <c r="E216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -4906,6 +5143,7 @@
       <c r="D217" s="3" t="n">
         <v>718036</v>
       </c>
+      <c r="E217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -4926,6 +5164,7 @@
       <c r="D218" s="3" t="n">
         <v>2703442</v>
       </c>
+      <c r="E218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -4946,6 +5185,7 @@
       <c r="D219" s="3" t="n">
         <v>3503699</v>
       </c>
+      <c r="E219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -4966,6 +5206,7 @@
       <c r="D220" s="3" t="n">
         <v>3503699</v>
       </c>
+      <c r="E220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -4986,6 +5227,7 @@
       <c r="D221" s="3" t="n">
         <v>4206052</v>
       </c>
+      <c r="E221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -5006,6 +5248,7 @@
       <c r="D222" s="3" t="n">
         <v>861182</v>
       </c>
+      <c r="E222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -5026,6 +5269,7 @@
       <c r="D223" s="3" t="n">
         <v>1446795</v>
       </c>
+      <c r="E223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -5046,6 +5290,7 @@
       <c r="D224" s="3" t="n">
         <v>1116631</v>
       </c>
+      <c r="E224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -5066,6 +5311,7 @@
       <c r="D225" s="3" t="n">
         <v>610862</v>
       </c>
+      <c r="E225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -5086,6 +5332,7 @@
       <c r="D226" s="3" t="n">
         <v>610862</v>
       </c>
+      <c r="E226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -5106,6 +5353,7 @@
       <c r="D227" s="3" t="n">
         <v>264854</v>
       </c>
+      <c r="E227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -5126,6 +5374,7 @@
       <c r="D228" s="3" t="n">
         <v>206681</v>
       </c>
+      <c r="E228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -5146,6 +5395,7 @@
       <c r="D229" s="3" t="n">
         <v>68126</v>
       </c>
+      <c r="E229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -5166,6 +5416,7 @@
       <c r="D230" s="3" t="n">
         <v>59706</v>
       </c>
+      <c r="E230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -5186,6 +5437,7 @@
       <c r="D231" s="3" t="n">
         <v>74250</v>
       </c>
+      <c r="E231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -5206,6 +5458,7 @@
       <c r="D232" s="3" t="n">
         <v>22963</v>
       </c>
+      <c r="E232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -5226,6 +5479,7 @@
       <c r="D233" s="3" t="n">
         <v>38268</v>
       </c>
+      <c r="E233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -5246,6 +5500,7 @@
       <c r="D234" s="3" t="n">
         <v>51664</v>
       </c>
+      <c r="E234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -5266,6 +5521,7 @@
       <c r="D235" s="3" t="n">
         <v>4405614</v>
       </c>
+      <c r="E235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -5286,6 +5542,7 @@
       <c r="D236" s="3" t="n">
         <v>20667</v>
       </c>
+      <c r="E236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -5306,6 +5563,7 @@
       <c r="D237" s="3" t="n">
         <v>1979964</v>
       </c>
+      <c r="E237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -5326,6 +5584,7 @@
       <c r="D238" s="3" t="n">
         <v>2260680</v>
       </c>
+      <c r="E238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -5346,6 +5605,7 @@
       <c r="D239" s="3" t="n">
         <v>3258588</v>
       </c>
+      <c r="E239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -5366,6 +5626,7 @@
       <c r="D240" s="3" t="n">
         <v>3342566</v>
       </c>
+      <c r="E240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -5386,6 +5647,7 @@
       <c r="D241" s="3" t="n">
         <v>3397144</v>
       </c>
+      <c r="E241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -5406,6 +5668,7 @@
       <c r="D242" s="3" t="n">
         <v>1222271</v>
       </c>
+      <c r="E242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -5426,6 +5689,7 @@
       <c r="D243" s="3" t="n">
         <v>1222271</v>
       </c>
+      <c r="E243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -5446,6 +5710,7 @@
       <c r="D244" s="3" t="n">
         <v>1261929</v>
       </c>
+      <c r="E244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -5466,6 +5731,7 @@
       <c r="D245" s="3" t="n">
         <v>1261929</v>
       </c>
+      <c r="E245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -5486,6 +5752,7 @@
       <c r="D246" s="3" t="n">
         <v>1261929</v>
       </c>
+      <c r="E246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -5506,6 +5773,7 @@
       <c r="D247" s="3" t="n">
         <v>1261929</v>
       </c>
+      <c r="E247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -5526,6 +5794,7 @@
       <c r="D248" s="3" t="n">
         <v>1234600</v>
       </c>
+      <c r="E248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -5546,6 +5815,7 @@
       <c r="D249" s="3" t="n">
         <v>1234600</v>
       </c>
+      <c r="E249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -5566,6 +5836,7 @@
       <c r="D250" s="3" t="n">
         <v>1234600</v>
       </c>
+      <c r="E250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -5586,6 +5857,7 @@
       <c r="D251" s="3" t="n">
         <v>1234600</v>
       </c>
+      <c r="E251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -5606,6 +5878,7 @@
       <c r="D252" s="3" t="n">
         <v>1371927</v>
       </c>
+      <c r="E252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -5626,6 +5899,7 @@
       <c r="D253" s="3" t="n">
         <v>1371927</v>
       </c>
+      <c r="E253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -5646,6 +5920,7 @@
       <c r="D254" s="3" t="n">
         <v>1453457</v>
       </c>
+      <c r="E254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -5666,6 +5941,7 @@
       <c r="D255" s="3" t="n">
         <v>1453457</v>
       </c>
+      <c r="E255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -5686,6 +5962,7 @@
       <c r="D256" s="3" t="n">
         <v>356857</v>
       </c>
+      <c r="E256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -5706,6 +5983,7 @@
       <c r="D257" s="3" t="n">
         <v>356857</v>
       </c>
+      <c r="E257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -5726,6 +6004,7 @@
       <c r="D258" s="3" t="n">
         <v>410457</v>
       </c>
+      <c r="E258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -5746,6 +6025,7 @@
       <c r="D259" s="3" t="n">
         <v>439849</v>
       </c>
+      <c r="E259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -5766,6 +6046,7 @@
       <c r="D260" s="3" t="n">
         <v>6391</v>
       </c>
+      <c r="E260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -5786,6 +6067,7 @@
       <c r="D261" s="3" t="n">
         <v>21320</v>
       </c>
+      <c r="E261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -5806,6 +6088,7 @@
       <c r="D262" s="3" t="n">
         <v>51664</v>
       </c>
+      <c r="E262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -5826,6 +6109,7 @@
       <c r="D263" s="3" t="n">
         <v>305122</v>
       </c>
+      <c r="E263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -5846,6 +6130,7 @@
       <c r="D264" s="3" t="n">
         <v>379990</v>
       </c>
+      <c r="E264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -5866,6 +6151,7 @@
       <c r="D265" s="3" t="n">
         <v>407471</v>
       </c>
+      <c r="E265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -5886,6 +6172,7 @@
       <c r="D266" s="3" t="n">
         <v>38116</v>
       </c>
+      <c r="E266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -5906,6 +6193,7 @@
       <c r="D267" s="3" t="n">
         <v>35363</v>
       </c>
+      <c r="E267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -5926,6 +6214,7 @@
       <c r="D268" s="3" t="n">
         <v>34135</v>
       </c>
+      <c r="E268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -5946,6 +6235,7 @@
       <c r="D269" s="3" t="n">
         <v>319400</v>
       </c>
+      <c r="E269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -5966,6 +6256,7 @@
       <c r="D270" s="3" t="n">
         <v>307805</v>
       </c>
+      <c r="E270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -5986,6 +6277,7 @@
       <c r="D271" s="3" t="n">
         <v>304707</v>
       </c>
+      <c r="E271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -6006,6 +6298,7 @@
       <c r="D272" s="3" t="n">
         <v>41761</v>
       </c>
+      <c r="E272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -6026,6 +6319,7 @@
       <c r="D273" s="3" t="n">
         <v>40982</v>
       </c>
+      <c r="E273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -6046,6 +6340,7 @@
       <c r="D274" s="3" t="n">
         <v>40212</v>
       </c>
+      <c r="E274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -6066,6 +6361,7 @@
       <c r="D275" s="3" t="n">
         <v>61862</v>
       </c>
+      <c r="E275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -6086,6 +6382,7 @@
       <c r="D276" s="3" t="n">
         <v>61862</v>
       </c>
+      <c r="E276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -6106,6 +6403,7 @@
       <c r="D277" s="3" t="n">
         <v>61862</v>
       </c>
+      <c r="E277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -6126,6 +6424,7 @@
       <c r="D278" s="3" t="n">
         <v>55675</v>
       </c>
+      <c r="E278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -6146,6 +6445,7 @@
       <c r="D279" s="3" t="n">
         <v>20880</v>
       </c>
+      <c r="E279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -6166,6 +6466,7 @@
       <c r="D280" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -6186,6 +6487,7 @@
       <c r="D281" s="3" t="n">
         <v>6532679</v>
       </c>
+      <c r="E281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -6206,6 +6508,7 @@
       <c r="D282" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -6226,6 +6529,7 @@
       <c r="D283" s="3" t="n">
         <v>6532679</v>
       </c>
+      <c r="E283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -6246,6 +6550,7 @@
       <c r="D284" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -6266,6 +6571,7 @@
       <c r="D285" s="3" t="n">
         <v>6431082</v>
       </c>
+      <c r="E285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -6286,6 +6592,7 @@
       <c r="D286" s="3" t="n">
         <v>6431082</v>
       </c>
+      <c r="E286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -6306,6 +6613,7 @@
       <c r="D287" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -6326,6 +6634,7 @@
       <c r="D288" s="3" t="n">
         <v>916925</v>
       </c>
+      <c r="E288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -6346,6 +6655,7 @@
       <c r="D289" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -6366,6 +6676,7 @@
       <c r="D290" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -6386,6 +6697,7 @@
       <c r="D291" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -6406,6 +6718,7 @@
       <c r="D292" s="3" t="n">
         <v>706164</v>
       </c>
+      <c r="E292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -6426,6 +6739,7 @@
       <c r="D293" s="3" t="n">
         <v>569294</v>
       </c>
+      <c r="E293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -6446,6 +6760,7 @@
       <c r="D294" s="3" t="n">
         <v>569294</v>
       </c>
+      <c r="E294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -6466,6 +6781,7 @@
       <c r="D295" s="3" t="n">
         <v>10866500</v>
       </c>
+      <c r="E295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -6486,6 +6802,7 @@
       <c r="D296" s="3" t="n">
         <v>13764331</v>
       </c>
+      <c r="E296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -6506,6 +6823,7 @@
       <c r="D297" s="3" t="n">
         <v>5447760</v>
       </c>
+      <c r="E297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -6526,6 +6844,7 @@
       <c r="D298" s="3" t="n">
         <v>3675100</v>
       </c>
+      <c r="E298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -6546,6 +6865,7 @@
       <c r="D299" s="3" t="n">
         <v>2143500</v>
       </c>
+      <c r="E299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -6566,6 +6886,7 @@
       <c r="D300" s="3" t="n">
         <v>903010</v>
       </c>
+      <c r="E300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -6586,6 +6907,7 @@
       <c r="D301" s="3" t="n">
         <v>728710</v>
       </c>
+      <c r="E301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -6606,6 +6928,7 @@
       <c r="D302" s="3" t="n">
         <v>11774430</v>
       </c>
+      <c r="E302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -6626,6 +6949,7 @@
       <c r="D303" s="3" t="n">
         <v>107182</v>
       </c>
+      <c r="E303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -6646,6 +6970,7 @@
       <c r="D304" s="3" t="n">
         <v>103955</v>
       </c>
+      <c r="E304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -6666,6 +6991,7 @@
       <c r="D305" s="3" t="n">
         <v>226712</v>
       </c>
+      <c r="E305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -6686,6 +7012,7 @@
       <c r="D306" s="3" t="n">
         <v>1034562</v>
       </c>
+      <c r="E306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -6706,6 +7033,7 @@
       <c r="D307" s="3" t="n">
         <v>9235</v>
       </c>
+      <c r="E307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -6726,6 +7054,7 @@
       <c r="D308" s="3" t="n">
         <v>1115572</v>
       </c>
+      <c r="E308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -6746,6 +7075,7 @@
       <c r="D309" s="3" t="n">
         <v>10866500</v>
       </c>
+      <c r="E309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -6766,6 +7096,7 @@
       <c r="D310" s="3" t="n">
         <v>1542850</v>
       </c>
+      <c r="E310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -6786,6 +7117,7 @@
       <c r="D311" s="3" t="n">
         <v>1542850</v>
       </c>
+      <c r="E311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -6806,6 +7138,7 @@
       <c r="D312" s="3" t="n">
         <v>1087347</v>
       </c>
+      <c r="E312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -6826,6 +7159,7 @@
       <c r="D313" s="3" t="n">
         <v>1087347</v>
       </c>
+      <c r="E313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -6846,6 +7180,7 @@
       <c r="D314" s="3" t="n">
         <v>1087347</v>
       </c>
+      <c r="E314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -6866,6 +7201,7 @@
       <c r="D315" s="3" t="n">
         <v>1087347</v>
       </c>
+      <c r="E315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -6886,6 +7222,7 @@
       <c r="D316" s="3" t="n">
         <v>182361</v>
       </c>
+      <c r="E316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -6906,6 +7243,7 @@
       <c r="D317" s="3" t="n">
         <v>703035</v>
       </c>
+      <c r="E317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -6926,6 +7264,7 @@
       <c r="D318" s="3" t="n">
         <v>703035</v>
       </c>
+      <c r="E318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -6946,6 +7285,7 @@
       <c r="D319" s="3" t="n">
         <v>783480</v>
       </c>
+      <c r="E319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -6966,6 +7306,7 @@
       <c r="D320" s="3" t="n">
         <v>28558</v>
       </c>
+      <c r="E320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -6986,6 +7327,7 @@
       <c r="D321" s="3" t="n">
         <v>28558</v>
       </c>
+      <c r="E321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -7006,6 +7348,7 @@
       <c r="D322" s="3" t="n">
         <v>1548670</v>
       </c>
+      <c r="E322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -7026,6 +7369,7 @@
       <c r="D323" s="3" t="n">
         <v>1226135</v>
       </c>
+      <c r="E323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -7046,6 +7390,7 @@
       <c r="D324" s="3" t="n">
         <v>1226135</v>
       </c>
+      <c r="E324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -7066,6 +7411,7 @@
       <c r="D325" s="3" t="n">
         <v>162930</v>
       </c>
+      <c r="E325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -7086,6 +7432,7 @@
       <c r="D326" s="3" t="n">
         <v>134368</v>
       </c>
+      <c r="E326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -7106,6 +7453,7 @@
       <c r="D327" s="3" t="n">
         <v>134368</v>
       </c>
+      <c r="E327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -7126,6 +7474,7 @@
       <c r="D328" s="3" t="n">
         <v>330012</v>
       </c>
+      <c r="E328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -7146,6 +7495,7 @@
       <c r="D329" s="3" t="n">
         <v>330012</v>
       </c>
+      <c r="E329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -7166,6 +7516,7 @@
       <c r="D330" s="3" t="n">
         <v>571913</v>
       </c>
+      <c r="E330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -7186,6 +7537,7 @@
       <c r="D331" s="3" t="n">
         <v>103076</v>
       </c>
+      <c r="E331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -7206,6 +7558,7 @@
       <c r="D332" s="3" t="n">
         <v>1464822</v>
       </c>
+      <c r="E332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -7226,6 +7579,7 @@
       <c r="D333" s="3" t="n">
         <v>1409011</v>
       </c>
+      <c r="E333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -7246,6 +7600,7 @@
       <c r="D334" s="3" t="n">
         <v>13273877</v>
       </c>
+      <c r="E334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -7266,6 +7621,7 @@
       <c r="D335" s="3" t="n">
         <v>7485191</v>
       </c>
+      <c r="E335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -7286,6 +7642,7 @@
       <c r="D336" s="3" t="n">
         <v>7485191</v>
       </c>
+      <c r="E336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -7306,6 +7663,7 @@
       <c r="D337" s="3" t="n">
         <v>6550486</v>
       </c>
+      <c r="E337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -7326,6 +7684,7 @@
       <c r="D338" s="3" t="n">
         <v>57296</v>
       </c>
+      <c r="E338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -7346,6 +7705,7 @@
       <c r="D339" s="3" t="n">
         <v>57296</v>
       </c>
+      <c r="E339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -7366,6 +7726,7 @@
       <c r="D340" s="3" t="n">
         <v>1703194</v>
       </c>
+      <c r="E340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -7386,6 +7747,7 @@
       <c r="D341" s="3" t="n">
         <v>1703194</v>
       </c>
+      <c r="E341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -7406,6 +7768,7 @@
       <c r="D342" s="3" t="n">
         <v>1703194</v>
       </c>
+      <c r="E342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -7426,6 +7789,7 @@
       <c r="D343" s="3" t="n">
         <v>1702044</v>
       </c>
+      <c r="E343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -7446,6 +7810,7 @@
       <c r="D344" s="3" t="n">
         <v>69427</v>
       </c>
+      <c r="E344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -7466,6 +7831,7 @@
       <c r="D345" s="3" t="n">
         <v>69427</v>
       </c>
+      <c r="E345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -7486,6 +7852,7 @@
       <c r="D346" s="3" t="n">
         <v>69427</v>
       </c>
+      <c r="E346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -7506,6 +7873,7 @@
       <c r="D347" s="3" t="n">
         <v>69427</v>
       </c>
+      <c r="E347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -7526,6 +7894,7 @@
       <c r="D348" s="3" t="n">
         <v>179164</v>
       </c>
+      <c r="E348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -7546,6 +7915,7 @@
       <c r="D349" s="3" t="n">
         <v>812737</v>
       </c>
+      <c r="E349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -7566,6 +7936,7 @@
       <c r="D350" s="3" t="n">
         <v>748230</v>
       </c>
+      <c r="E350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -7586,6 +7957,7 @@
       <c r="D351" s="3" t="n">
         <v>748230</v>
       </c>
+      <c r="E351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -7606,6 +7978,7 @@
       <c r="D352" s="3" t="n">
         <v>89187</v>
       </c>
+      <c r="E352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -7626,6 +7999,7 @@
       <c r="D353" s="3" t="n">
         <v>89187</v>
       </c>
+      <c r="E353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -7646,6 +8020,7 @@
       <c r="D354" s="3" t="n">
         <v>165886</v>
       </c>
+      <c r="E354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -7666,6 +8041,7 @@
       <c r="D355" s="3" t="n">
         <v>165886</v>
       </c>
+      <c r="E355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -7686,6 +8062,7 @@
       <c r="D356" s="3" t="n">
         <v>157516</v>
       </c>
+      <c r="E356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -7706,6 +8083,7 @@
       <c r="D357" s="3" t="n">
         <v>157516</v>
       </c>
+      <c r="E357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -7726,6 +8104,7 @@
       <c r="D358" s="3" t="n">
         <v>1545370</v>
       </c>
+      <c r="E358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -7746,6 +8125,7 @@
       <c r="D359" s="3" t="n">
         <v>195348</v>
       </c>
+      <c r="E359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -7766,6 +8146,7 @@
       <c r="D360" s="3" t="n">
         <v>2089541</v>
       </c>
+      <c r="E360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -7786,6 +8167,7 @@
       <c r="D361" s="3" t="n">
         <v>1240266</v>
       </c>
+      <c r="E361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -7806,6 +8188,7 @@
       <c r="D362" s="3" t="n">
         <v>63828</v>
       </c>
+      <c r="E362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -7826,6 +8209,7 @@
       <c r="D363" s="3" t="n">
         <v>53745</v>
       </c>
+      <c r="E363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -7846,6 +8230,7 @@
       <c r="D364" s="3" t="n">
         <v>1205352</v>
       </c>
+      <c r="E364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -7866,6 +8251,7 @@
       <c r="D365" s="3" t="n">
         <v>959291</v>
       </c>
+      <c r="E365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -7886,6 +8272,7 @@
       <c r="D366" s="3" t="n">
         <v>959291</v>
       </c>
+      <c r="E366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -7906,6 +8293,7 @@
       <c r="D367" s="3" t="n">
         <v>556957</v>
       </c>
+      <c r="E367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -7926,6 +8314,7 @@
       <c r="D368" s="3" t="n">
         <v>433922</v>
       </c>
+      <c r="E368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -7946,6 +8335,7 @@
       <c r="D369" s="3" t="n">
         <v>433922</v>
       </c>
+      <c r="E369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -7966,6 +8356,7 @@
       <c r="D370" s="3" t="n">
         <v>562699</v>
       </c>
+      <c r="E370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -7986,6 +8377,7 @@
       <c r="D371" s="3" t="n">
         <v>438395</v>
       </c>
+      <c r="E371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -8006,6 +8398,7 @@
       <c r="D372" s="3" t="n">
         <v>438395</v>
       </c>
+      <c r="E372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -8026,6 +8419,7 @@
       <c r="D373" s="3" t="n">
         <v>379604</v>
       </c>
+      <c r="E373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -8046,6 +8440,7 @@
       <c r="D374" s="3" t="n">
         <v>73230</v>
       </c>
+      <c r="E374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -8066,6 +8461,7 @@
       <c r="D375" s="3" t="n">
         <v>509787</v>
       </c>
+      <c r="E375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -8086,6 +8482,7 @@
       <c r="D376" s="3" t="n">
         <v>554292</v>
       </c>
+      <c r="E376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -8106,6 +8503,7 @@
       <c r="D377" s="3" t="n">
         <v>181486</v>
       </c>
+      <c r="E377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -8126,6 +8524,7 @@
       <c r="D378" s="3" t="n">
         <v>509787</v>
       </c>
+      <c r="E378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -8146,6 +8545,7 @@
       <c r="D379" s="3" t="n">
         <v>1306769</v>
       </c>
+      <c r="E379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -8166,6 +8566,7 @@
       <c r="D380" s="3" t="n">
         <v>554292</v>
       </c>
+      <c r="E380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -8186,6 +8587,7 @@
       <c r="D381" s="3" t="n">
         <v>67498</v>
       </c>
+      <c r="E381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -8206,6 +8608,7 @@
       <c r="D382" s="3" t="n">
         <v>50704</v>
       </c>
+      <c r="E382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -8226,6 +8629,7 @@
       <c r="D383" s="3" t="n">
         <v>50704</v>
       </c>
+      <c r="E383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -8246,6 +8650,7 @@
       <c r="D384" s="3" t="n">
         <v>601842</v>
       </c>
+      <c r="E384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -8266,6 +8671,7 @@
       <c r="D385" s="3" t="n">
         <v>601842</v>
       </c>
+      <c r="E385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -8286,6 +8692,7 @@
       <c r="D386" s="3" t="n">
         <v>255000</v>
       </c>
+      <c r="E386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -8306,6 +8713,7 @@
       <c r="D387" s="3" t="n">
         <v>328515</v>
       </c>
+      <c r="E387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -8326,6 +8734,7 @@
       <c r="D388" s="3" t="n">
         <v>402029</v>
       </c>
+      <c r="E388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -8346,6 +8755,7 @@
       <c r="D389" s="3" t="n">
         <v>475552</v>
       </c>
+      <c r="E389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -8366,6 +8776,7 @@
       <c r="D390" s="3" t="n">
         <v>549067</v>
       </c>
+      <c r="E390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -8386,6 +8797,7 @@
       <c r="D391" s="3" t="n">
         <v>623343</v>
       </c>
+      <c r="E391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -8406,6 +8818,7 @@
       <c r="D392" s="3" t="n">
         <v>696857</v>
       </c>
+      <c r="E392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -8426,6 +8839,7 @@
       <c r="D393" s="3" t="n">
         <v>770372</v>
       </c>
+      <c r="E393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -8446,6 +8860,7 @@
       <c r="D394" s="3" t="n">
         <v>843895</v>
       </c>
+      <c r="E394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -8466,6 +8881,7 @@
       <c r="D395" s="3" t="n">
         <v>208286</v>
       </c>
+      <c r="E395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -8486,6 +8902,7 @@
       <c r="D396" s="3" t="n">
         <v>288695</v>
       </c>
+      <c r="E396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -8506,6 +8923,7 @@
       <c r="D397" s="3" t="n">
         <v>369105</v>
       </c>
+      <c r="E397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -8526,6 +8944,7 @@
       <c r="D398" s="3" t="n">
         <v>449514</v>
       </c>
+      <c r="E398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -8546,6 +8965,7 @@
       <c r="D399" s="3" t="n">
         <v>530686</v>
       </c>
+      <c r="E399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -8566,6 +8986,7 @@
       <c r="D400" s="3" t="n">
         <v>611095</v>
       </c>
+      <c r="E400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -8586,6 +9007,7 @@
       <c r="D401" s="3" t="n">
         <v>186848</v>
       </c>
+      <c r="E401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -8606,6 +9028,7 @@
       <c r="D402" s="3" t="n">
         <v>264953</v>
       </c>
+      <c r="E402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -8626,6 +9049,7 @@
       <c r="D403" s="3" t="n">
         <v>343067</v>
       </c>
+      <c r="E403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -8646,6 +9070,7 @@
       <c r="D404" s="3" t="n">
         <v>420410</v>
       </c>
+      <c r="E404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -8666,6 +9091,7 @@
       <c r="D405" s="3" t="n">
         <v>498524</v>
       </c>
+      <c r="E405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -8686,6 +9112,7 @@
       <c r="D406" s="3" t="n">
         <v>575867</v>
       </c>
+      <c r="E406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -8706,6 +9133,7 @@
       <c r="D407" s="3" t="n">
         <v>653972</v>
       </c>
+      <c r="E407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -8726,6 +9154,7 @@
       <c r="D408" s="3" t="n">
         <v>731324</v>
       </c>
+      <c r="E408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -8746,6 +9175,7 @@
       <c r="D409" s="3" t="n">
         <v>808667</v>
       </c>
+      <c r="E409" s="2" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -8766,6 +9196,7 @@
       <c r="D410" s="3" t="n">
         <v>886772</v>
       </c>
+      <c r="E410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -8786,6 +9217,7 @@
       <c r="D411" s="3" t="n">
         <v>214419</v>
       </c>
+      <c r="E411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -8806,6 +9238,7 @@
       <c r="D412" s="3" t="n">
         <v>299419</v>
       </c>
+      <c r="E412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -8826,6 +9259,7 @@
       <c r="D413" s="3" t="n">
         <v>383648</v>
       </c>
+      <c r="E413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -8846,6 +9280,7 @@
       <c r="D414" s="3" t="n">
         <v>20783</v>
       </c>
+      <c r="E414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -8866,6 +9301,7 @@
       <c r="D415" s="3" t="n">
         <v>26220</v>
       </c>
+      <c r="E415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -8886,6 +9322,7 @@
       <c r="D416" s="3" t="n">
         <v>44175</v>
       </c>
+      <c r="E416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -8906,6 +9343,7 @@
       <c r="D417" s="3" t="n">
         <v>43070</v>
       </c>
+      <c r="E417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -8926,6 +9364,7 @@
       <c r="D418" s="3" t="n">
         <v>72756</v>
       </c>
+      <c r="E418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -8946,6 +9385,7 @@
       <c r="D419" s="3" t="n">
         <v>332618</v>
       </c>
+      <c r="E419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -8966,6 +9406,7 @@
       <c r="D420" s="3" t="n">
         <v>46820</v>
       </c>
+      <c r="E420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -8986,6 +9427,7 @@
       <c r="D421" s="3" t="n">
         <v>46774</v>
       </c>
+      <c r="E421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -9006,6 +9448,7 @@
       <c r="D422" s="3" t="n">
         <v>83152</v>
       </c>
+      <c r="E422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -9026,6 +9469,7 @@
       <c r="D423" s="3" t="n">
         <v>62359</v>
       </c>
+      <c r="E423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -9046,6 +9490,7 @@
       <c r="D424" s="3" t="n">
         <v>62359</v>
       </c>
+      <c r="E424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -9066,6 +9511,7 @@
       <c r="D425" s="3" t="n">
         <v>102206</v>
       </c>
+      <c r="E425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -9086,6 +9532,7 @@
       <c r="D426" s="3" t="n">
         <v>102206</v>
       </c>
+      <c r="E426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -9106,6 +9553,7 @@
       <c r="D427" s="3" t="n">
         <v>291948</v>
       </c>
+      <c r="E427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -9126,6 +9574,7 @@
       <c r="D428" s="3" t="n">
         <v>16333</v>
       </c>
+      <c r="E428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -9146,6 +9595,7 @@
       <c r="D429" s="3" t="n">
         <v>11432</v>
       </c>
+      <c r="E429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -9166,6 +9616,7 @@
       <c r="D430" s="3" t="n">
         <v>36385</v>
       </c>
+      <c r="E430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -9186,6 +9637,7 @@
       <c r="D431" s="3" t="n">
         <v>5836</v>
       </c>
+      <c r="E431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -9206,6 +9658,7 @@
       <c r="D432" s="3" t="n">
         <v>6465</v>
       </c>
+      <c r="E432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -9226,6 +9679,7 @@
       <c r="D433" s="3" t="n">
         <v>67919</v>
       </c>
+      <c r="E433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -9246,6 +9700,7 @@
       <c r="D434" s="3" t="n">
         <v>1519807</v>
       </c>
+      <c r="E434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -9266,6 +9721,7 @@
       <c r="D435" s="3" t="n">
         <v>65893</v>
       </c>
+      <c r="E435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -9286,6 +9742,7 @@
       <c r="D436" s="3" t="n">
         <v>250243</v>
       </c>
+      <c r="E436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -9306,6 +9763,7 @@
       <c r="D437" s="3" t="n">
         <v>2497</v>
       </c>
+      <c r="E437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -9326,6 +9784,7 @@
       <c r="D438" s="3" t="n">
         <v>5004</v>
       </c>
+      <c r="E438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -9346,6 +9805,7 @@
       <c r="D439" s="3" t="n">
         <v>8334</v>
       </c>
+      <c r="E439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -9366,6 +9826,7 @@
       <c r="D440" s="3" t="n">
         <v>15012</v>
       </c>
+      <c r="E440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -9386,6 +9847,7 @@
       <c r="D441" s="3" t="n">
         <v>583</v>
       </c>
+      <c r="E441" s="2" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -9406,6 +9868,7 @@
       <c r="D442" s="3" t="n">
         <v>7187030</v>
       </c>
+      <c r="E442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -9426,6 +9889,7 @@
       <c r="D443" s="3" t="n">
         <v>8738110</v>
       </c>
+      <c r="E443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -9446,6 +9910,7 @@
       <c r="D444" s="3" t="n">
         <v>13804820</v>
       </c>
+      <c r="E444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -9466,6 +9931,7 @@
       <c r="D445" s="3" t="n">
         <v>17633830</v>
       </c>
+      <c r="E445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -9486,6 +9952,7 @@
       <c r="D446" s="3" t="n">
         <v>2701838</v>
       </c>
+      <c r="E446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -9506,6 +9973,7 @@
       <c r="D447" s="3" t="n">
         <v>215612</v>
       </c>
+      <c r="E447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -9526,6 +9994,7 @@
       <c r="D448" s="3" t="n">
         <v>56783</v>
       </c>
+      <c r="E448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -9546,6 +10015,7 @@
       <c r="D449" s="3" t="n">
         <v>264415</v>
       </c>
+      <c r="E449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -9566,6 +10036,7 @@
       <c r="D450" s="3" t="n">
         <v>7489396</v>
       </c>
+      <c r="E450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -9586,6 +10057,7 @@
       <c r="D451" s="3" t="n">
         <v>1794121</v>
       </c>
+      <c r="E451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -9606,6 +10078,7 @@
       <c r="D452" s="3" t="n">
         <v>1794121</v>
       </c>
+      <c r="E452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -9626,6 +10099,7 @@
       <c r="D453" s="3" t="n">
         <v>755703</v>
       </c>
+      <c r="E453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -9646,6 +10120,7 @@
       <c r="D454" s="3" t="n">
         <v>768249</v>
       </c>
+      <c r="E454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -9666,6 +10141,7 @@
       <c r="D455" s="3" t="n">
         <v>75296</v>
       </c>
+      <c r="E455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -9686,6 +10162,7 @@
       <c r="D456" s="3" t="n">
         <v>29577</v>
       </c>
+      <c r="E456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -9706,6 +10183,7 @@
       <c r="D457" s="3" t="n">
         <v>260863</v>
       </c>
+      <c r="E457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -9726,6 +10204,7 @@
       <c r="D458" s="3" t="n">
         <v>645441</v>
       </c>
+      <c r="E458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -9746,6 +10225,7 @@
       <c r="D459" s="3" t="n">
         <v>735086</v>
       </c>
+      <c r="E459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -9766,6 +10246,7 @@
       <c r="D460" s="3" t="n">
         <v>641518</v>
       </c>
+      <c r="E460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -9786,6 +10267,7 @@
       <c r="D461" s="3" t="n">
         <v>645441</v>
       </c>
+      <c r="E461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -9806,6 +10288,7 @@
       <c r="D462" s="3" t="n">
         <v>645441</v>
       </c>
+      <c r="E462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -9826,6 +10309,7 @@
       <c r="D463" s="3" t="n">
         <v>735086</v>
       </c>
+      <c r="E463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -9846,6 +10330,7 @@
       <c r="D464" s="3" t="n">
         <v>641518</v>
       </c>
+      <c r="E464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -9866,6 +10351,7 @@
       <c r="D465" s="3" t="n">
         <v>735086</v>
       </c>
+      <c r="E465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -9886,6 +10372,7 @@
       <c r="D466" s="3" t="n">
         <v>641518</v>
       </c>
+      <c r="E466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -9906,6 +10393,7 @@
       <c r="D467" s="3" t="n">
         <v>1870424</v>
       </c>
+      <c r="E467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -9926,6 +10414,7 @@
       <c r="D468" s="3" t="n">
         <v>1870424</v>
       </c>
+      <c r="E468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -9946,6 +10435,7 @@
       <c r="D469" s="3" t="n">
         <v>290449</v>
       </c>
+      <c r="E469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -9966,6 +10456,7 @@
       <c r="D470" s="3" t="n">
         <v>88748</v>
       </c>
+      <c r="E470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -9986,6 +10477,7 @@
       <c r="D471" s="3" t="n">
         <v>37648</v>
       </c>
+      <c r="E471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -10006,6 +10498,7 @@
       <c r="D472" s="3" t="n">
         <v>645441</v>
       </c>
+      <c r="E472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -10026,6 +10519,7 @@
       <c r="D473" s="3" t="n">
         <v>735086</v>
       </c>
+      <c r="E473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -10046,6 +10540,7 @@
       <c r="D474" s="3" t="n">
         <v>641518</v>
       </c>
+      <c r="E474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -10066,6 +10561,7 @@
       <c r="D475" s="3" t="n">
         <v>137298</v>
       </c>
+      <c r="E475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
@@ -10086,6 +10582,7 @@
       <c r="D476" s="3" t="n">
         <v>7911208</v>
       </c>
+      <c r="E476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
@@ -10106,6 +10603,7 @@
       <c r="D477" s="3" t="n">
         <v>2984898</v>
       </c>
+      <c r="E477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
@@ -10126,6 +10624,7 @@
       <c r="D478" s="3" t="n">
         <v>5211108</v>
       </c>
+      <c r="E478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
@@ -10146,6 +10645,7 @@
       <c r="D479" s="3" t="n">
         <v>3301512</v>
       </c>
+      <c r="E479" s="2" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
@@ -10166,6 +10666,7 @@
       <c r="D480" s="3" t="n">
         <v>2176663</v>
       </c>
+      <c r="E480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
@@ -10186,6 +10687,7 @@
       <c r="D481" s="3" t="n">
         <v>2112641</v>
       </c>
+      <c r="E481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
@@ -10206,6 +10708,7 @@
       <c r="D482" s="3" t="n">
         <v>212401</v>
       </c>
+      <c r="E482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
@@ -10226,6 +10729,7 @@
       <c r="D483" s="3" t="n">
         <v>311102</v>
       </c>
+      <c r="E483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
@@ -10246,6 +10750,7 @@
       <c r="D484" s="3" t="n">
         <v>7491044</v>
       </c>
+      <c r="E484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
@@ -10266,6 +10771,7 @@
       <c r="D485" s="3" t="n">
         <v>4588310</v>
       </c>
+      <c r="E485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
@@ -10286,6 +10792,7 @@
       <c r="D486" s="3" t="n">
         <v>4863056</v>
       </c>
+      <c r="E486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
@@ -10306,6 +10813,7 @@
       <c r="D487" s="3" t="n">
         <v>3550012</v>
       </c>
+      <c r="E487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
@@ -10323,8 +10831,13 @@
           <t>CER_8GHz_11GHz_6+0_SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D488" s="3" t="n">
+      <c r="D488" s="5" t="n">
         <v>1826945</v>
+      </c>
+      <c r="E488" s="4" t="inlineStr">
+        <is>
+          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
+        </is>
       </c>
     </row>
     <row r="489">
@@ -10343,8 +10856,13 @@
           <t>CER_8GHz_11GHz_6+0_Non SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D489" s="3" t="n">
+      <c r="D489" s="5" t="n">
         <v>2449121</v>
+      </c>
+      <c r="E489" s="4" t="inlineStr">
+        <is>
+          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
+        </is>
       </c>
     </row>
     <row r="490">
@@ -10363,8 +10881,13 @@
           <t>CER_8GHz_11GHz_8+0_SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D490" s="3" t="n">
+      <c r="D490" s="5" t="n">
         <v>326933</v>
+      </c>
+      <c r="E490" s="4" t="inlineStr">
+        <is>
+          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
+        </is>
       </c>
     </row>
     <row r="491">
@@ -10383,8 +10906,13 @@
           <t>CER_8GHz_11GHz_8+0_Non SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D491" s="3" t="n">
+      <c r="D491" s="5" t="n">
         <v>901776</v>
+      </c>
+      <c r="E491" s="4" t="inlineStr">
+        <is>
+          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
+        </is>
       </c>
     </row>
     <row r="492">
@@ -10406,6 +10934,7 @@
       <c r="D492" s="3" t="n">
         <v>9524845</v>
       </c>
+      <c r="E492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
@@ -10426,6 +10955,7 @@
       <c r="D493" s="3" t="n">
         <v>312186</v>
       </c>
+      <c r="E493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
@@ -10446,9 +10976,10 @@
       <c r="D494" s="3" t="n">
         <v>312186</v>
       </c>
+      <c r="E494" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D494"/>
+  <autoFilter ref="A1:E494"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/17_전송망설계팀_판매단가_안내.xlsx
+++ b/output/17_전송망설계팀_판매단가_안내.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체493종_판매단가_제시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체493종_판매단가_제시'!$A$1:$E$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'판매단가_안내(초안)'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'전체493종_판매단가_제시'!$A$1:$D$494</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -92,9 +92,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -462,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -505,7 +502,6 @@
 KT commerce 이돈현입니다.
 금번 8GHz/11GHz 대역 MW 장비(Ceragon) 전체 493개 품목의 판매단가를 K코드 단위로 정리해 첨부(전체493종_판매단가_제시 시트)해 드립니다. 단가는 EA(단품) 기준입니다.
 위 단가는 당사 표준 마진 정책(장비군별 2~5%)을 반영해 산정하였습니다. 산정 근거가 필요하시면 말씀해 주시면 상세 자료를 공유드리겠습니다.
-다만 4개 품목(K9213027~030, 8/11GHz 6+0/8+0 구성 SW패키지)은 공급사 측 가격 구조를 확인 중이라 잠정치입니다 - 확인 완료 후 갱신된 단가로 다시 안내드리겠습니다.
 검토 후 문의사항 있으시면 편하게 연락 주세요.
 감사합니다.
 KT commerce 이돈현 드림</t>
@@ -539,29 +535,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>확인 중 4개 품목(내부용)</t>
+          <t>주의</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>K9213027~030(8/11GHz 6+0/8+0 SD·Non_SD SW패키지)는 SD가 Non_SD보다 싼 역전 현상이 있어 대성에 확인 요청 중(18번 파일). 이 4개만 '확인 중(잠정치)'로 표시하고 나머지 489개는 그대로 전달 - 근거가 이 4개에 국한돼 전체를 늦출 필요는 없다는 판단.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>주의</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
           <t>이 초안은 자동 생성된 것이니 보내시기 전에 실제 상황(호칭, 첨부 형식, 일정 등)에 맞게 다듬어서 사용하시기 바랍니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B7"/>
+  <autoFilter ref="A1:B6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -572,14 +556,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E494"/>
+  <dimension ref="A1:D494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -603,11 +586,6 @@
           <t>판매단가(EA)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -628,7 +606,6 @@
       <c r="D2" s="3" t="n">
         <v>510332</v>
       </c>
-      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -649,7 +626,6 @@
       <c r="D3" s="3" t="n">
         <v>299159</v>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -670,7 +646,6 @@
       <c r="D4" s="3" t="n">
         <v>299159</v>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -691,7 +666,6 @@
       <c r="D5" s="3" t="n">
         <v>281558</v>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -712,7 +686,6 @@
       <c r="D6" s="3" t="n">
         <v>14688</v>
       </c>
-      <c r="E6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -733,7 +706,6 @@
       <c r="D7" s="3" t="n">
         <v>356409</v>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -754,7 +726,6 @@
       <c r="D8" s="3" t="n">
         <v>263958</v>
       </c>
-      <c r="E8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -775,7 +746,6 @@
       <c r="D9" s="3" t="n">
         <v>249486</v>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -796,7 +766,6 @@
       <c r="D10" s="3" t="n">
         <v>398882</v>
       </c>
-      <c r="E10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -817,7 +786,6 @@
       <c r="D11" s="3" t="n">
         <v>398882</v>
       </c>
-      <c r="E11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -838,7 +806,6 @@
       <c r="D12" s="3" t="n">
         <v>375417</v>
       </c>
-      <c r="E12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -859,7 +826,6 @@
       <c r="D13" s="3" t="n">
         <v>346080</v>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -880,7 +846,6 @@
       <c r="D14" s="3" t="n">
         <v>451675</v>
       </c>
-      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -901,7 +866,6 @@
       <c r="D15" s="3" t="n">
         <v>451675</v>
       </c>
-      <c r="E15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -922,7 +886,6 @@
       <c r="D16" s="3" t="n">
         <v>428210</v>
       </c>
-      <c r="E16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -943,7 +906,6 @@
       <c r="D17" s="3" t="n">
         <v>398882</v>
       </c>
-      <c r="E17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -964,7 +926,6 @@
       <c r="D18" s="3" t="n">
         <v>627656</v>
       </c>
-      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -985,7 +946,6 @@
       <c r="D19" s="3" t="n">
         <v>627656</v>
       </c>
-      <c r="E19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1006,7 +966,6 @@
       <c r="D20" s="3" t="n">
         <v>586590</v>
       </c>
-      <c r="E20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1027,7 +986,6 @@
       <c r="D21" s="3" t="n">
         <v>533797</v>
       </c>
-      <c r="E21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1048,7 +1006,6 @@
       <c r="D22" s="3" t="n">
         <v>395534</v>
       </c>
-      <c r="E22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1069,7 +1026,6 @@
       <c r="D23" s="3" t="n">
         <v>395534</v>
       </c>
-      <c r="E23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1090,7 +1046,6 @@
       <c r="D24" s="3" t="n">
         <v>395534</v>
       </c>
-      <c r="E24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1111,7 +1066,6 @@
       <c r="D25" s="3" t="n">
         <v>395534</v>
       </c>
-      <c r="E25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1132,7 +1086,6 @@
       <c r="D26" s="3" t="n">
         <v>46920</v>
       </c>
-      <c r="E26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1153,7 +1106,6 @@
       <c r="D27" s="3" t="n">
         <v>46920</v>
       </c>
-      <c r="E27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1174,7 +1126,6 @@
       <c r="D28" s="3" t="n">
         <v>41056</v>
       </c>
-      <c r="E28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1195,7 +1146,6 @@
       <c r="D29" s="3" t="n">
         <v>588271</v>
       </c>
-      <c r="E29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1216,7 +1166,6 @@
       <c r="D30" s="3" t="n">
         <v>58808</v>
       </c>
-      <c r="E30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1237,7 +1186,6 @@
       <c r="D31" s="3" t="n">
         <v>779066</v>
       </c>
-      <c r="E31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1258,7 +1206,6 @@
       <c r="D32" s="3" t="n">
         <v>228101</v>
       </c>
-      <c r="E32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1279,7 +1226,6 @@
       <c r="D33" s="3" t="n">
         <v>228101</v>
       </c>
-      <c r="E33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1300,7 +1246,6 @@
       <c r="D34" s="3" t="n">
         <v>228101</v>
       </c>
-      <c r="E34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1321,7 +1266,6 @@
       <c r="D35" s="3" t="n">
         <v>228101</v>
       </c>
-      <c r="E35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1342,7 +1286,6 @@
       <c r="D36" s="3" t="n">
         <v>215325</v>
       </c>
-      <c r="E36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1363,7 +1306,6 @@
       <c r="D37" s="3" t="n">
         <v>215325</v>
       </c>
-      <c r="E37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1384,7 +1326,6 @@
       <c r="D38" s="3" t="n">
         <v>207020</v>
       </c>
-      <c r="E38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1405,7 +1346,6 @@
       <c r="D39" s="3" t="n">
         <v>187533</v>
       </c>
-      <c r="E39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1426,7 +1366,6 @@
       <c r="D40" s="3" t="n">
         <v>187533</v>
       </c>
-      <c r="E40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1447,7 +1386,6 @@
       <c r="D41" s="3" t="n">
         <v>187533</v>
       </c>
-      <c r="E41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1468,7 +1406,6 @@
       <c r="D42" s="3" t="n">
         <v>297007</v>
       </c>
-      <c r="E42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1489,7 +1426,6 @@
       <c r="D43" s="3" t="n">
         <v>297007</v>
       </c>
-      <c r="E43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1510,7 +1446,6 @@
       <c r="D44" s="3" t="n">
         <v>297007</v>
       </c>
-      <c r="E44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1531,7 +1466,6 @@
       <c r="D45" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1552,7 +1486,6 @@
       <c r="D46" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1573,7 +1506,6 @@
       <c r="D47" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1594,7 +1526,6 @@
       <c r="D48" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1615,7 +1546,6 @@
       <c r="D49" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1636,7 +1566,6 @@
       <c r="D50" s="3" t="n">
         <v>2723025</v>
       </c>
-      <c r="E50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1657,7 +1586,6 @@
       <c r="D51" s="3" t="n">
         <v>3107955</v>
       </c>
-      <c r="E51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1678,7 +1606,6 @@
       <c r="D52" s="3" t="n">
         <v>3107955</v>
       </c>
-      <c r="E52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1699,7 +1626,6 @@
       <c r="D53" s="3" t="n">
         <v>3043793</v>
       </c>
-      <c r="E53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1720,7 +1646,6 @@
       <c r="D54" s="3" t="n">
         <v>3043793</v>
       </c>
-      <c r="E54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1741,7 +1666,6 @@
       <c r="D55" s="3" t="n">
         <v>3043793</v>
       </c>
-      <c r="E55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1762,7 +1686,6 @@
       <c r="D56" s="3" t="n">
         <v>3371697</v>
       </c>
-      <c r="E56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1783,7 +1706,6 @@
       <c r="D57" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1804,7 +1726,6 @@
       <c r="D58" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1825,7 +1746,6 @@
       <c r="D59" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1846,7 +1766,6 @@
       <c r="D60" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1867,7 +1786,6 @@
       <c r="D61" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1888,7 +1806,6 @@
       <c r="D62" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1909,7 +1826,6 @@
       <c r="D63" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1930,7 +1846,6 @@
       <c r="D64" s="3" t="n">
         <v>684314</v>
       </c>
-      <c r="E64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1951,7 +1866,6 @@
       <c r="D65" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1972,7 +1886,6 @@
       <c r="D66" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1993,7 +1906,6 @@
       <c r="D67" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -2014,7 +1926,6 @@
       <c r="D68" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -2035,7 +1946,6 @@
       <c r="D69" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -2056,7 +1966,6 @@
       <c r="D70" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2077,7 +1986,6 @@
       <c r="D71" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2098,7 +2006,6 @@
       <c r="D72" s="3" t="n">
         <v>969440</v>
       </c>
-      <c r="E72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2119,7 +2026,6 @@
       <c r="D73" s="3" t="n">
         <v>172831</v>
       </c>
-      <c r="E73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2140,7 +2046,6 @@
       <c r="D74" s="3" t="n">
         <v>24227</v>
       </c>
-      <c r="E74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2161,7 +2066,6 @@
       <c r="D75" s="3" t="n">
         <v>24227</v>
       </c>
-      <c r="E75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2182,7 +2086,6 @@
       <c r="D76" s="3" t="n">
         <v>24227</v>
       </c>
-      <c r="E76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2203,7 +2106,6 @@
       <c r="D77" s="3" t="n">
         <v>78401</v>
       </c>
-      <c r="E77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2224,7 +2126,6 @@
       <c r="D78" s="3" t="n">
         <v>78401</v>
       </c>
-      <c r="E78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2245,7 +2146,6 @@
       <c r="D79" s="3" t="n">
         <v>78401</v>
       </c>
-      <c r="E79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2266,7 +2166,6 @@
       <c r="D80" s="3" t="n">
         <v>63220</v>
       </c>
-      <c r="E80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2287,7 +2186,6 @@
       <c r="D81" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2308,7 +2206,6 @@
       <c r="D82" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2329,7 +2226,6 @@
       <c r="D83" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2350,7 +2246,6 @@
       <c r="D84" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2371,7 +2266,6 @@
       <c r="D85" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2392,7 +2286,6 @@
       <c r="D86" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2413,7 +2306,6 @@
       <c r="D87" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2434,7 +2326,6 @@
       <c r="D88" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2455,7 +2346,6 @@
       <c r="D89" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2476,7 +2366,6 @@
       <c r="D90" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2497,7 +2386,6 @@
       <c r="D91" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2518,7 +2406,6 @@
       <c r="D92" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2539,7 +2426,6 @@
       <c r="D93" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2560,7 +2446,6 @@
       <c r="D94" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2581,7 +2466,6 @@
       <c r="D95" s="3" t="n">
         <v>3494770</v>
       </c>
-      <c r="E95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2602,7 +2486,6 @@
       <c r="D96" s="3" t="n">
         <v>3494770</v>
       </c>
-      <c r="E96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2623,7 +2506,6 @@
       <c r="D97" s="3" t="n">
         <v>3494770</v>
       </c>
-      <c r="E97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2644,7 +2526,6 @@
       <c r="D98" s="3" t="n">
         <v>3494770</v>
       </c>
-      <c r="E98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2665,7 +2546,6 @@
       <c r="D99" s="3" t="n">
         <v>4919190</v>
       </c>
-      <c r="E99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2686,7 +2566,6 @@
       <c r="D100" s="3" t="n">
         <v>4919190</v>
       </c>
-      <c r="E100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2707,7 +2586,6 @@
       <c r="D101" s="3" t="n">
         <v>4919190</v>
       </c>
-      <c r="E101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2728,7 +2606,6 @@
       <c r="D102" s="3" t="n">
         <v>4919190</v>
       </c>
-      <c r="E102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2749,7 +2626,6 @@
       <c r="D103" s="3" t="n">
         <v>6542350</v>
       </c>
-      <c r="E103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2770,7 +2646,6 @@
       <c r="D104" s="3" t="n">
         <v>6542350</v>
       </c>
-      <c r="E104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2791,7 +2666,6 @@
       <c r="D105" s="3" t="n">
         <v>6542350</v>
       </c>
-      <c r="E105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2812,7 +2686,6 @@
       <c r="D106" s="3" t="n">
         <v>6542350</v>
       </c>
-      <c r="E106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2833,7 +2706,6 @@
       <c r="D107" s="3" t="n">
         <v>8631560</v>
       </c>
-      <c r="E107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2854,7 +2726,6 @@
       <c r="D108" s="3" t="n">
         <v>8631560</v>
       </c>
-      <c r="E108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2875,7 +2746,6 @@
       <c r="D109" s="3" t="n">
         <v>8631560</v>
       </c>
-      <c r="E109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2896,7 +2766,6 @@
       <c r="D110" s="3" t="n">
         <v>8631560</v>
       </c>
-      <c r="E110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2917,7 +2786,6 @@
       <c r="D111" s="3" t="n">
         <v>10927020</v>
       </c>
-      <c r="E111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2938,7 +2806,6 @@
       <c r="D112" s="3" t="n">
         <v>10927020</v>
       </c>
-      <c r="E112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2959,7 +2826,6 @@
       <c r="D113" s="3" t="n">
         <v>10927020</v>
       </c>
-      <c r="E113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2980,7 +2846,6 @@
       <c r="D114" s="3" t="n">
         <v>10927020</v>
       </c>
-      <c r="E114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -3001,7 +2866,6 @@
       <c r="D115" s="3" t="n">
         <v>14163130</v>
       </c>
-      <c r="E115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -3022,7 +2886,6 @@
       <c r="D116" s="3" t="n">
         <v>14163130</v>
       </c>
-      <c r="E116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3043,7 +2906,6 @@
       <c r="D117" s="3" t="n">
         <v>14163130</v>
       </c>
-      <c r="E117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3064,7 +2926,6 @@
       <c r="D118" s="3" t="n">
         <v>14163130</v>
       </c>
-      <c r="E118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3085,7 +2946,6 @@
       <c r="D119" s="3" t="n">
         <v>23761213</v>
       </c>
-      <c r="E119" s="2" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3106,7 +2966,6 @@
       <c r="D120" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E120" s="2" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3127,7 +2986,6 @@
       <c r="D121" s="3" t="n">
         <v>2970144</v>
       </c>
-      <c r="E121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3148,7 +3006,6 @@
       <c r="D122" s="3" t="n">
         <v>5343190</v>
       </c>
-      <c r="E122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3169,7 +3026,6 @@
       <c r="D123" s="3" t="n">
         <v>5343190</v>
       </c>
-      <c r="E123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3190,7 +3046,6 @@
       <c r="D124" s="3" t="n">
         <v>5343190</v>
       </c>
-      <c r="E124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3211,7 +3066,6 @@
       <c r="D125" s="3" t="n">
         <v>491844</v>
       </c>
-      <c r="E125" s="2" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3232,7 +3086,6 @@
       <c r="D126" s="3" t="n">
         <v>491844</v>
       </c>
-      <c r="E126" s="2" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3253,7 +3106,6 @@
       <c r="D127" s="3" t="n">
         <v>491844</v>
       </c>
-      <c r="E127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3274,7 +3126,6 @@
       <c r="D128" s="3" t="n">
         <v>288770</v>
       </c>
-      <c r="E128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3295,7 +3146,6 @@
       <c r="D129" s="3" t="n">
         <v>288770</v>
       </c>
-      <c r="E129" s="2" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3316,7 +3166,6 @@
       <c r="D130" s="3" t="n">
         <v>288770</v>
       </c>
-      <c r="E130" s="2" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3337,7 +3186,6 @@
       <c r="D131" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E131" s="2" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3358,7 +3206,6 @@
       <c r="D132" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E132" s="2" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3379,7 +3226,6 @@
       <c r="D133" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3400,7 +3246,6 @@
       <c r="D134" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E134" s="2" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3421,7 +3266,6 @@
       <c r="D135" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E135" s="2" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3442,7 +3286,6 @@
       <c r="D136" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E136" s="2" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3463,7 +3306,6 @@
       <c r="D137" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3484,7 +3326,6 @@
       <c r="D138" s="3" t="n">
         <v>1746438</v>
       </c>
-      <c r="E138" s="2" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3505,7 +3346,6 @@
       <c r="D139" s="3" t="n">
         <v>201637</v>
       </c>
-      <c r="E139" s="2" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3526,7 +3366,6 @@
       <c r="D140" s="3" t="n">
         <v>206699</v>
       </c>
-      <c r="E140" s="2" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3547,7 +3386,6 @@
       <c r="D141" s="3" t="n">
         <v>206699</v>
       </c>
-      <c r="E141" s="2" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3568,7 +3406,6 @@
       <c r="D142" s="3" t="n">
         <v>206699</v>
       </c>
-      <c r="E142" s="2" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3589,7 +3426,6 @@
       <c r="D143" s="3" t="n">
         <v>206699</v>
       </c>
-      <c r="E143" s="2" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3610,7 +3446,6 @@
       <c r="D144" s="3" t="n">
         <v>491844</v>
       </c>
-      <c r="E144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3631,7 +3466,6 @@
       <c r="D145" s="3" t="n">
         <v>491844</v>
       </c>
-      <c r="E145" s="2" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3652,7 +3486,6 @@
       <c r="D146" s="3" t="n">
         <v>484291</v>
       </c>
-      <c r="E146" s="2" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3673,7 +3506,6 @@
       <c r="D147" s="3" t="n">
         <v>110473</v>
       </c>
-      <c r="E147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3694,7 +3526,6 @@
       <c r="D148" s="3" t="n">
         <v>110473</v>
       </c>
-      <c r="E148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3715,7 +3546,6 @@
       <c r="D149" s="3" t="n">
         <v>110473</v>
       </c>
-      <c r="E149" s="2" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3736,7 +3566,6 @@
       <c r="D150" s="3" t="n">
         <v>49171</v>
       </c>
-      <c r="E150" s="2" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -3757,7 +3586,6 @@
       <c r="D151" s="3" t="n">
         <v>49171</v>
       </c>
-      <c r="E151" s="2" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -3778,7 +3606,6 @@
       <c r="D152" s="3" t="n">
         <v>49171</v>
       </c>
-      <c r="E152" s="2" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -3799,7 +3626,6 @@
       <c r="D153" s="3" t="n">
         <v>108025</v>
       </c>
-      <c r="E153" s="2" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -3820,7 +3646,6 @@
       <c r="D154" s="3" t="n">
         <v>677185</v>
       </c>
-      <c r="E154" s="2" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -3841,7 +3666,6 @@
       <c r="D155" s="3" t="n">
         <v>677185</v>
       </c>
-      <c r="E155" s="2" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -3862,7 +3686,6 @@
       <c r="D156" s="3" t="n">
         <v>677185</v>
       </c>
-      <c r="E156" s="2" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -3883,7 +3706,6 @@
       <c r="D157" s="3" t="n">
         <v>727676</v>
       </c>
-      <c r="E157" s="2" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -3904,7 +3726,6 @@
       <c r="D158" s="3" t="n">
         <v>727676</v>
       </c>
-      <c r="E158" s="2" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -3925,7 +3746,6 @@
       <c r="D159" s="3" t="n">
         <v>727676</v>
       </c>
-      <c r="E159" s="2" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -3946,7 +3766,6 @@
       <c r="D160" s="3" t="n">
         <v>727676</v>
       </c>
-      <c r="E160" s="2" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -3967,7 +3786,6 @@
       <c r="D161" s="3" t="n">
         <v>1410357</v>
       </c>
-      <c r="E161" s="2" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -3988,7 +3806,6 @@
       <c r="D162" s="3" t="n">
         <v>1410357</v>
       </c>
-      <c r="E162" s="2" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -4009,7 +3826,6 @@
       <c r="D163" s="3" t="n">
         <v>1410357</v>
       </c>
-      <c r="E163" s="2" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -4030,7 +3846,6 @@
       <c r="D164" s="3" t="n">
         <v>1410357</v>
       </c>
-      <c r="E164" s="2" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -4051,7 +3866,6 @@
       <c r="D165" s="3" t="n">
         <v>2739692</v>
       </c>
-      <c r="E165" s="2" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -4072,7 +3886,6 @@
       <c r="D166" s="3" t="n">
         <v>3024380</v>
       </c>
-      <c r="E166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -4093,7 +3906,6 @@
       <c r="D167" s="3" t="n">
         <v>3024380</v>
       </c>
-      <c r="E167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -4114,7 +3926,6 @@
       <c r="D168" s="3" t="n">
         <v>3024380</v>
       </c>
-      <c r="E168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -4135,7 +3946,6 @@
       <c r="D169" s="3" t="n">
         <v>5343190</v>
       </c>
-      <c r="E169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -4156,7 +3966,6 @@
       <c r="D170" s="3" t="n">
         <v>7343</v>
       </c>
-      <c r="E170" s="2" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -4177,7 +3986,6 @@
       <c r="D171" s="3" t="n">
         <v>29395</v>
       </c>
-      <c r="E171" s="2" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -4198,7 +4006,6 @@
       <c r="D172" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E172" s="2" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -4219,7 +4026,6 @@
       <c r="D173" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E173" s="2" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -4240,7 +4046,6 @@
       <c r="D174" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E174" s="2" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -4261,7 +4066,6 @@
       <c r="D175" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E175" s="2" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -4282,7 +4086,6 @@
       <c r="D176" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E176" s="2" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -4303,7 +4106,6 @@
       <c r="D177" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E177" s="2" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -4324,7 +4126,6 @@
       <c r="D178" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E178" s="2" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -4345,7 +4146,6 @@
       <c r="D179" s="3" t="n">
         <v>11581111</v>
       </c>
-      <c r="E179" s="2" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -4366,7 +4166,6 @@
       <c r="D180" s="3" t="n">
         <v>106621</v>
       </c>
-      <c r="E180" s="2" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -4387,7 +4186,6 @@
       <c r="D181" s="3" t="n">
         <v>835520</v>
       </c>
-      <c r="E181" s="2" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -4408,7 +4206,6 @@
       <c r="D182" s="3" t="n">
         <v>1035827</v>
       </c>
-      <c r="E182" s="2" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -4429,7 +4226,6 @@
       <c r="D183" s="3" t="n">
         <v>835520</v>
       </c>
-      <c r="E183" s="2" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -4450,7 +4246,6 @@
       <c r="D184" s="3" t="n">
         <v>1035827</v>
       </c>
-      <c r="E184" s="2" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -4471,7 +4266,6 @@
       <c r="D185" s="3" t="n">
         <v>102906</v>
       </c>
-      <c r="E185" s="2" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -4492,7 +4286,6 @@
       <c r="D186" s="3" t="n">
         <v>102924</v>
       </c>
-      <c r="E186" s="2" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -4513,7 +4306,6 @@
       <c r="D187" s="3" t="n">
         <v>56066</v>
       </c>
-      <c r="E187" s="2" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -4534,7 +4326,6 @@
       <c r="D188" s="3" t="n">
         <v>397635</v>
       </c>
-      <c r="E188" s="2" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -4555,7 +4346,6 @@
       <c r="D189" s="3" t="n">
         <v>113037</v>
       </c>
-      <c r="E189" s="2" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -4576,7 +4366,6 @@
       <c r="D190" s="3" t="n">
         <v>118946</v>
       </c>
-      <c r="E190" s="2" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -4597,7 +4386,6 @@
       <c r="D191" s="3" t="n">
         <v>217181</v>
       </c>
-      <c r="E191" s="2" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -4618,7 +4406,6 @@
       <c r="D192" s="3" t="n">
         <v>26176</v>
       </c>
-      <c r="E192" s="2" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -4639,7 +4426,6 @@
       <c r="D193" s="3" t="n">
         <v>10670</v>
       </c>
-      <c r="E193" s="2" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -4660,7 +4446,6 @@
       <c r="D194" s="3" t="n">
         <v>3326</v>
       </c>
-      <c r="E194" s="2" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -4681,7 +4466,6 @@
       <c r="D195" s="3" t="n">
         <v>52595</v>
       </c>
-      <c r="E195" s="2" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -4702,7 +4486,6 @@
       <c r="D196" s="3" t="n">
         <v>47597</v>
       </c>
-      <c r="E196" s="2" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -4723,7 +4506,6 @@
       <c r="D197" s="3" t="n">
         <v>641536</v>
       </c>
-      <c r="E197" s="2" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -4744,7 +4526,6 @@
       <c r="D198" s="3" t="n">
         <v>454428</v>
       </c>
-      <c r="E198" s="2" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -4765,7 +4546,6 @@
       <c r="D199" s="3" t="n">
         <v>230540</v>
       </c>
-      <c r="E199" s="2" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -4786,7 +4566,6 @@
       <c r="D200" s="3" t="n">
         <v>162379</v>
       </c>
-      <c r="E200" s="2" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -4807,7 +4586,6 @@
       <c r="D201" s="3" t="n">
         <v>149019</v>
       </c>
-      <c r="E201" s="2" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -4828,7 +4606,6 @@
       <c r="D202" s="3" t="n">
         <v>149019</v>
       </c>
-      <c r="E202" s="2" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -4849,7 +4626,6 @@
       <c r="D203" s="3" t="n">
         <v>132306</v>
       </c>
-      <c r="E203" s="2" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -4870,7 +4646,6 @@
       <c r="D204" s="3" t="n">
         <v>193124</v>
       </c>
-      <c r="E204" s="2" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -4891,7 +4666,6 @@
       <c r="D205" s="3" t="n">
         <v>483191</v>
       </c>
-      <c r="E205" s="2" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -4912,7 +4686,6 @@
       <c r="D206" s="3" t="n">
         <v>573930</v>
       </c>
-      <c r="E206" s="2" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -4933,7 +4706,6 @@
       <c r="D207" s="3" t="n">
         <v>633313</v>
       </c>
-      <c r="E207" s="2" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -4954,7 +4726,6 @@
       <c r="D208" s="3" t="n">
         <v>2612516</v>
       </c>
-      <c r="E208" s="2" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -4975,7 +4746,6 @@
       <c r="D209" s="3" t="n">
         <v>163571</v>
       </c>
-      <c r="E209" s="2" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -4996,7 +4766,6 @@
       <c r="D210" s="3" t="n">
         <v>170171</v>
       </c>
-      <c r="E210" s="2" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -5017,7 +4786,6 @@
       <c r="D211" s="3" t="n">
         <v>4754</v>
       </c>
-      <c r="E211" s="2" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -5038,7 +4806,6 @@
       <c r="D212" s="3" t="n">
         <v>7899</v>
       </c>
-      <c r="E212" s="2" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -5059,7 +4826,6 @@
       <c r="D213" s="3" t="n">
         <v>17000</v>
       </c>
-      <c r="E213" s="2" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -5080,7 +4846,6 @@
       <c r="D214" s="3" t="n">
         <v>56057</v>
       </c>
-      <c r="E214" s="2" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -5101,7 +4866,6 @@
       <c r="D215" s="3" t="n">
         <v>219900</v>
       </c>
-      <c r="E215" s="2" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -5122,7 +4886,6 @@
       <c r="D216" s="3" t="n">
         <v>467716</v>
       </c>
-      <c r="E216" s="2" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -5143,7 +4906,6 @@
       <c r="D217" s="3" t="n">
         <v>718036</v>
       </c>
-      <c r="E217" s="2" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -5164,7 +4926,6 @@
       <c r="D218" s="3" t="n">
         <v>2703442</v>
       </c>
-      <c r="E218" s="2" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -5185,7 +4946,6 @@
       <c r="D219" s="3" t="n">
         <v>3503699</v>
       </c>
-      <c r="E219" s="2" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -5206,7 +4966,6 @@
       <c r="D220" s="3" t="n">
         <v>3503699</v>
       </c>
-      <c r="E220" s="2" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -5227,7 +4986,6 @@
       <c r="D221" s="3" t="n">
         <v>4206052</v>
       </c>
-      <c r="E221" s="2" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -5248,7 +5006,6 @@
       <c r="D222" s="3" t="n">
         <v>861182</v>
       </c>
-      <c r="E222" s="2" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -5269,7 +5026,6 @@
       <c r="D223" s="3" t="n">
         <v>1446795</v>
       </c>
-      <c r="E223" s="2" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -5290,7 +5046,6 @@
       <c r="D224" s="3" t="n">
         <v>1116631</v>
       </c>
-      <c r="E224" s="2" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -5311,7 +5066,6 @@
       <c r="D225" s="3" t="n">
         <v>610862</v>
       </c>
-      <c r="E225" s="2" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -5332,7 +5086,6 @@
       <c r="D226" s="3" t="n">
         <v>610862</v>
       </c>
-      <c r="E226" s="2" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -5353,7 +5106,6 @@
       <c r="D227" s="3" t="n">
         <v>264854</v>
       </c>
-      <c r="E227" s="2" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -5374,7 +5126,6 @@
       <c r="D228" s="3" t="n">
         <v>206681</v>
       </c>
-      <c r="E228" s="2" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -5395,7 +5146,6 @@
       <c r="D229" s="3" t="n">
         <v>68126</v>
       </c>
-      <c r="E229" s="2" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -5416,7 +5166,6 @@
       <c r="D230" s="3" t="n">
         <v>59706</v>
       </c>
-      <c r="E230" s="2" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -5437,7 +5186,6 @@
       <c r="D231" s="3" t="n">
         <v>74250</v>
       </c>
-      <c r="E231" s="2" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -5458,7 +5206,6 @@
       <c r="D232" s="3" t="n">
         <v>22963</v>
       </c>
-      <c r="E232" s="2" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -5479,7 +5226,6 @@
       <c r="D233" s="3" t="n">
         <v>38268</v>
       </c>
-      <c r="E233" s="2" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -5500,7 +5246,6 @@
       <c r="D234" s="3" t="n">
         <v>51664</v>
       </c>
-      <c r="E234" s="2" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -5521,7 +5266,6 @@
       <c r="D235" s="3" t="n">
         <v>4405614</v>
       </c>
-      <c r="E235" s="2" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -5542,7 +5286,6 @@
       <c r="D236" s="3" t="n">
         <v>20667</v>
       </c>
-      <c r="E236" s="2" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -5563,7 +5306,6 @@
       <c r="D237" s="3" t="n">
         <v>1979964</v>
       </c>
-      <c r="E237" s="2" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -5584,7 +5326,6 @@
       <c r="D238" s="3" t="n">
         <v>2260680</v>
       </c>
-      <c r="E238" s="2" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -5605,7 +5346,6 @@
       <c r="D239" s="3" t="n">
         <v>3258588</v>
       </c>
-      <c r="E239" s="2" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -5626,7 +5366,6 @@
       <c r="D240" s="3" t="n">
         <v>3342566</v>
       </c>
-      <c r="E240" s="2" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -5647,7 +5386,6 @@
       <c r="D241" s="3" t="n">
         <v>3397144</v>
       </c>
-      <c r="E241" s="2" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -5668,7 +5406,6 @@
       <c r="D242" s="3" t="n">
         <v>1222271</v>
       </c>
-      <c r="E242" s="2" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -5689,7 +5426,6 @@
       <c r="D243" s="3" t="n">
         <v>1222271</v>
       </c>
-      <c r="E243" s="2" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -5710,7 +5446,6 @@
       <c r="D244" s="3" t="n">
         <v>1261929</v>
       </c>
-      <c r="E244" s="2" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -5731,7 +5466,6 @@
       <c r="D245" s="3" t="n">
         <v>1261929</v>
       </c>
-      <c r="E245" s="2" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -5752,7 +5486,6 @@
       <c r="D246" s="3" t="n">
         <v>1261929</v>
       </c>
-      <c r="E246" s="2" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -5773,7 +5506,6 @@
       <c r="D247" s="3" t="n">
         <v>1261929</v>
       </c>
-      <c r="E247" s="2" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -5794,7 +5526,6 @@
       <c r="D248" s="3" t="n">
         <v>1234600</v>
       </c>
-      <c r="E248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -5815,7 +5546,6 @@
       <c r="D249" s="3" t="n">
         <v>1234600</v>
       </c>
-      <c r="E249" s="2" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -5836,7 +5566,6 @@
       <c r="D250" s="3" t="n">
         <v>1234600</v>
       </c>
-      <c r="E250" s="2" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -5857,7 +5586,6 @@
       <c r="D251" s="3" t="n">
         <v>1234600</v>
       </c>
-      <c r="E251" s="2" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -5878,7 +5606,6 @@
       <c r="D252" s="3" t="n">
         <v>1371927</v>
       </c>
-      <c r="E252" s="2" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -5899,7 +5626,6 @@
       <c r="D253" s="3" t="n">
         <v>1371927</v>
       </c>
-      <c r="E253" s="2" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -5920,7 +5646,6 @@
       <c r="D254" s="3" t="n">
         <v>1453457</v>
       </c>
-      <c r="E254" s="2" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -5941,7 +5666,6 @@
       <c r="D255" s="3" t="n">
         <v>1453457</v>
       </c>
-      <c r="E255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -5962,7 +5686,6 @@
       <c r="D256" s="3" t="n">
         <v>356857</v>
       </c>
-      <c r="E256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -5983,7 +5706,6 @@
       <c r="D257" s="3" t="n">
         <v>356857</v>
       </c>
-      <c r="E257" s="2" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -6004,7 +5726,6 @@
       <c r="D258" s="3" t="n">
         <v>410457</v>
       </c>
-      <c r="E258" s="2" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -6025,7 +5746,6 @@
       <c r="D259" s="3" t="n">
         <v>439849</v>
       </c>
-      <c r="E259" s="2" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -6046,7 +5766,6 @@
       <c r="D260" s="3" t="n">
         <v>6391</v>
       </c>
-      <c r="E260" s="2" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -6067,7 +5786,6 @@
       <c r="D261" s="3" t="n">
         <v>21320</v>
       </c>
-      <c r="E261" s="2" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -6088,7 +5806,6 @@
       <c r="D262" s="3" t="n">
         <v>51664</v>
       </c>
-      <c r="E262" s="2" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -6109,7 +5826,6 @@
       <c r="D263" s="3" t="n">
         <v>305122</v>
       </c>
-      <c r="E263" s="2" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -6130,7 +5846,6 @@
       <c r="D264" s="3" t="n">
         <v>379990</v>
       </c>
-      <c r="E264" s="2" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -6151,7 +5866,6 @@
       <c r="D265" s="3" t="n">
         <v>407471</v>
       </c>
-      <c r="E265" s="2" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -6172,7 +5886,6 @@
       <c r="D266" s="3" t="n">
         <v>38116</v>
       </c>
-      <c r="E266" s="2" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -6193,7 +5906,6 @@
       <c r="D267" s="3" t="n">
         <v>35363</v>
       </c>
-      <c r="E267" s="2" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -6214,7 +5926,6 @@
       <c r="D268" s="3" t="n">
         <v>34135</v>
       </c>
-      <c r="E268" s="2" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -6235,7 +5946,6 @@
       <c r="D269" s="3" t="n">
         <v>319400</v>
       </c>
-      <c r="E269" s="2" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -6256,7 +5966,6 @@
       <c r="D270" s="3" t="n">
         <v>307805</v>
       </c>
-      <c r="E270" s="2" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -6277,7 +5986,6 @@
       <c r="D271" s="3" t="n">
         <v>304707</v>
       </c>
-      <c r="E271" s="2" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -6298,7 +6006,6 @@
       <c r="D272" s="3" t="n">
         <v>41761</v>
       </c>
-      <c r="E272" s="2" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -6319,7 +6026,6 @@
       <c r="D273" s="3" t="n">
         <v>40982</v>
       </c>
-      <c r="E273" s="2" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -6340,7 +6046,6 @@
       <c r="D274" s="3" t="n">
         <v>40212</v>
       </c>
-      <c r="E274" s="2" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -6361,7 +6066,6 @@
       <c r="D275" s="3" t="n">
         <v>61862</v>
       </c>
-      <c r="E275" s="2" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -6382,7 +6086,6 @@
       <c r="D276" s="3" t="n">
         <v>61862</v>
       </c>
-      <c r="E276" s="2" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -6403,7 +6106,6 @@
       <c r="D277" s="3" t="n">
         <v>61862</v>
       </c>
-      <c r="E277" s="2" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -6424,7 +6126,6 @@
       <c r="D278" s="3" t="n">
         <v>55675</v>
       </c>
-      <c r="E278" s="2" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -6445,7 +6146,6 @@
       <c r="D279" s="3" t="n">
         <v>20880</v>
       </c>
-      <c r="E279" s="2" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -6466,7 +6166,6 @@
       <c r="D280" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E280" s="2" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -6487,7 +6186,6 @@
       <c r="D281" s="3" t="n">
         <v>6532679</v>
       </c>
-      <c r="E281" s="2" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -6508,7 +6206,6 @@
       <c r="D282" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E282" s="2" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -6529,7 +6226,6 @@
       <c r="D283" s="3" t="n">
         <v>6532679</v>
       </c>
-      <c r="E283" s="2" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -6550,7 +6246,6 @@
       <c r="D284" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E284" s="2" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -6571,7 +6266,6 @@
       <c r="D285" s="3" t="n">
         <v>6431082</v>
       </c>
-      <c r="E285" s="2" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -6592,7 +6286,6 @@
       <c r="D286" s="3" t="n">
         <v>6431082</v>
       </c>
-      <c r="E286" s="2" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -6613,7 +6306,6 @@
       <c r="D287" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E287" s="2" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -6634,7 +6326,6 @@
       <c r="D288" s="3" t="n">
         <v>916925</v>
       </c>
-      <c r="E288" s="2" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
@@ -6655,7 +6346,6 @@
       <c r="D289" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E289" s="2" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
@@ -6676,7 +6366,6 @@
       <c r="D290" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E290" s="2" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
@@ -6697,7 +6386,6 @@
       <c r="D291" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E291" s="2" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
@@ -6718,7 +6406,6 @@
       <c r="D292" s="3" t="n">
         <v>706164</v>
       </c>
-      <c r="E292" s="2" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
@@ -6739,7 +6426,6 @@
       <c r="D293" s="3" t="n">
         <v>569294</v>
       </c>
-      <c r="E293" s="2" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -6760,7 +6446,6 @@
       <c r="D294" s="3" t="n">
         <v>569294</v>
       </c>
-      <c r="E294" s="2" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -6781,7 +6466,6 @@
       <c r="D295" s="3" t="n">
         <v>10866500</v>
       </c>
-      <c r="E295" s="2" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -6802,7 +6486,6 @@
       <c r="D296" s="3" t="n">
         <v>13764331</v>
       </c>
-      <c r="E296" s="2" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -6823,7 +6506,6 @@
       <c r="D297" s="3" t="n">
         <v>5447760</v>
       </c>
-      <c r="E297" s="2" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
@@ -6844,7 +6526,6 @@
       <c r="D298" s="3" t="n">
         <v>3675100</v>
       </c>
-      <c r="E298" s="2" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
@@ -6865,7 +6546,6 @@
       <c r="D299" s="3" t="n">
         <v>2143500</v>
       </c>
-      <c r="E299" s="2" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
@@ -6886,7 +6566,6 @@
       <c r="D300" s="3" t="n">
         <v>903010</v>
       </c>
-      <c r="E300" s="2" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
@@ -6907,7 +6586,6 @@
       <c r="D301" s="3" t="n">
         <v>728710</v>
       </c>
-      <c r="E301" s="2" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
@@ -6928,7 +6606,6 @@
       <c r="D302" s="3" t="n">
         <v>11774430</v>
       </c>
-      <c r="E302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -6949,7 +6626,6 @@
       <c r="D303" s="3" t="n">
         <v>107182</v>
       </c>
-      <c r="E303" s="2" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
@@ -6970,7 +6646,6 @@
       <c r="D304" s="3" t="n">
         <v>103955</v>
       </c>
-      <c r="E304" s="2" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
@@ -6991,7 +6666,6 @@
       <c r="D305" s="3" t="n">
         <v>226712</v>
       </c>
-      <c r="E305" s="2" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
@@ -7012,7 +6686,6 @@
       <c r="D306" s="3" t="n">
         <v>1034562</v>
       </c>
-      <c r="E306" s="2" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
@@ -7033,7 +6706,6 @@
       <c r="D307" s="3" t="n">
         <v>9235</v>
       </c>
-      <c r="E307" s="2" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -7054,7 +6726,6 @@
       <c r="D308" s="3" t="n">
         <v>1115572</v>
       </c>
-      <c r="E308" s="2" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -7075,7 +6746,6 @@
       <c r="D309" s="3" t="n">
         <v>10866500</v>
       </c>
-      <c r="E309" s="2" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -7096,7 +6766,6 @@
       <c r="D310" s="3" t="n">
         <v>1542850</v>
       </c>
-      <c r="E310" s="2" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
@@ -7117,7 +6786,6 @@
       <c r="D311" s="3" t="n">
         <v>1542850</v>
       </c>
-      <c r="E311" s="2" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -7138,7 +6806,6 @@
       <c r="D312" s="3" t="n">
         <v>1087347</v>
       </c>
-      <c r="E312" s="2" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -7159,7 +6826,6 @@
       <c r="D313" s="3" t="n">
         <v>1087347</v>
       </c>
-      <c r="E313" s="2" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
@@ -7180,7 +6846,6 @@
       <c r="D314" s="3" t="n">
         <v>1087347</v>
       </c>
-      <c r="E314" s="2" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
@@ -7201,7 +6866,6 @@
       <c r="D315" s="3" t="n">
         <v>1087347</v>
       </c>
-      <c r="E315" s="2" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -7222,7 +6886,6 @@
       <c r="D316" s="3" t="n">
         <v>182361</v>
       </c>
-      <c r="E316" s="2" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -7243,7 +6906,6 @@
       <c r="D317" s="3" t="n">
         <v>703035</v>
       </c>
-      <c r="E317" s="2" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
@@ -7264,7 +6926,6 @@
       <c r="D318" s="3" t="n">
         <v>703035</v>
       </c>
-      <c r="E318" s="2" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
@@ -7285,7 +6946,6 @@
       <c r="D319" s="3" t="n">
         <v>783480</v>
       </c>
-      <c r="E319" s="2" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
@@ -7306,7 +6966,6 @@
       <c r="D320" s="3" t="n">
         <v>28558</v>
       </c>
-      <c r="E320" s="2" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -7327,7 +6986,6 @@
       <c r="D321" s="3" t="n">
         <v>28558</v>
       </c>
-      <c r="E321" s="2" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
@@ -7348,7 +7006,6 @@
       <c r="D322" s="3" t="n">
         <v>1548670</v>
       </c>
-      <c r="E322" s="2" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
@@ -7369,7 +7026,6 @@
       <c r="D323" s="3" t="n">
         <v>1226135</v>
       </c>
-      <c r="E323" s="2" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -7390,7 +7046,6 @@
       <c r="D324" s="3" t="n">
         <v>1226135</v>
       </c>
-      <c r="E324" s="2" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
@@ -7411,7 +7066,6 @@
       <c r="D325" s="3" t="n">
         <v>162930</v>
       </c>
-      <c r="E325" s="2" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -7432,7 +7086,6 @@
       <c r="D326" s="3" t="n">
         <v>134368</v>
       </c>
-      <c r="E326" s="2" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
@@ -7453,7 +7106,6 @@
       <c r="D327" s="3" t="n">
         <v>134368</v>
       </c>
-      <c r="E327" s="2" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
@@ -7474,7 +7126,6 @@
       <c r="D328" s="3" t="n">
         <v>330012</v>
       </c>
-      <c r="E328" s="2" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
@@ -7495,7 +7146,6 @@
       <c r="D329" s="3" t="n">
         <v>330012</v>
       </c>
-      <c r="E329" s="2" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -7516,7 +7166,6 @@
       <c r="D330" s="3" t="n">
         <v>571913</v>
       </c>
-      <c r="E330" s="2" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
@@ -7537,7 +7186,6 @@
       <c r="D331" s="3" t="n">
         <v>103076</v>
       </c>
-      <c r="E331" s="2" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
@@ -7558,7 +7206,6 @@
       <c r="D332" s="3" t="n">
         <v>1464822</v>
       </c>
-      <c r="E332" s="2" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -7579,7 +7226,6 @@
       <c r="D333" s="3" t="n">
         <v>1409011</v>
       </c>
-      <c r="E333" s="2" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
@@ -7600,7 +7246,6 @@
       <c r="D334" s="3" t="n">
         <v>13273877</v>
       </c>
-      <c r="E334" s="2" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -7621,7 +7266,6 @@
       <c r="D335" s="3" t="n">
         <v>7485191</v>
       </c>
-      <c r="E335" s="2" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -7642,7 +7286,6 @@
       <c r="D336" s="3" t="n">
         <v>7485191</v>
       </c>
-      <c r="E336" s="2" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
@@ -7663,7 +7306,6 @@
       <c r="D337" s="3" t="n">
         <v>6550486</v>
       </c>
-      <c r="E337" s="2" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -7684,7 +7326,6 @@
       <c r="D338" s="3" t="n">
         <v>57296</v>
       </c>
-      <c r="E338" s="2" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -7705,7 +7346,6 @@
       <c r="D339" s="3" t="n">
         <v>57296</v>
       </c>
-      <c r="E339" s="2" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
@@ -7726,7 +7366,6 @@
       <c r="D340" s="3" t="n">
         <v>1703194</v>
       </c>
-      <c r="E340" s="2" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
@@ -7747,7 +7386,6 @@
       <c r="D341" s="3" t="n">
         <v>1703194</v>
       </c>
-      <c r="E341" s="2" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
@@ -7768,7 +7406,6 @@
       <c r="D342" s="3" t="n">
         <v>1703194</v>
       </c>
-      <c r="E342" s="2" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
@@ -7789,7 +7426,6 @@
       <c r="D343" s="3" t="n">
         <v>1702044</v>
       </c>
-      <c r="E343" s="2" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -7810,7 +7446,6 @@
       <c r="D344" s="3" t="n">
         <v>69427</v>
       </c>
-      <c r="E344" s="2" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
@@ -7831,7 +7466,6 @@
       <c r="D345" s="3" t="n">
         <v>69427</v>
       </c>
-      <c r="E345" s="2" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -7852,7 +7486,6 @@
       <c r="D346" s="3" t="n">
         <v>69427</v>
       </c>
-      <c r="E346" s="2" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -7873,7 +7506,6 @@
       <c r="D347" s="3" t="n">
         <v>69427</v>
       </c>
-      <c r="E347" s="2" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -7894,7 +7526,6 @@
       <c r="D348" s="3" t="n">
         <v>179164</v>
       </c>
-      <c r="E348" s="2" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
@@ -7915,7 +7546,6 @@
       <c r="D349" s="3" t="n">
         <v>812737</v>
       </c>
-      <c r="E349" s="2" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
@@ -7936,7 +7566,6 @@
       <c r="D350" s="3" t="n">
         <v>748230</v>
       </c>
-      <c r="E350" s="2" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
@@ -7957,7 +7586,6 @@
       <c r="D351" s="3" t="n">
         <v>748230</v>
       </c>
-      <c r="E351" s="2" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
@@ -7978,7 +7606,6 @@
       <c r="D352" s="3" t="n">
         <v>89187</v>
       </c>
-      <c r="E352" s="2" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -7999,7 +7626,6 @@
       <c r="D353" s="3" t="n">
         <v>89187</v>
       </c>
-      <c r="E353" s="2" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
@@ -8020,7 +7646,6 @@
       <c r="D354" s="3" t="n">
         <v>165886</v>
       </c>
-      <c r="E354" s="2" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
@@ -8041,7 +7666,6 @@
       <c r="D355" s="3" t="n">
         <v>165886</v>
       </c>
-      <c r="E355" s="2" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
@@ -8062,7 +7686,6 @@
       <c r="D356" s="3" t="n">
         <v>157516</v>
       </c>
-      <c r="E356" s="2" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -8083,7 +7706,6 @@
       <c r="D357" s="3" t="n">
         <v>157516</v>
       </c>
-      <c r="E357" s="2" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" s="2" t="inlineStr">
@@ -8104,7 +7726,6 @@
       <c r="D358" s="3" t="n">
         <v>1545370</v>
       </c>
-      <c r="E358" s="2" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" s="2" t="inlineStr">
@@ -8125,7 +7746,6 @@
       <c r="D359" s="3" t="n">
         <v>195348</v>
       </c>
-      <c r="E359" s="2" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -8146,7 +7766,6 @@
       <c r="D360" s="3" t="n">
         <v>2089541</v>
       </c>
-      <c r="E360" s="2" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" s="2" t="inlineStr">
@@ -8167,7 +7786,6 @@
       <c r="D361" s="3" t="n">
         <v>1240266</v>
       </c>
-      <c r="E361" s="2" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -8188,7 +7806,6 @@
       <c r="D362" s="3" t="n">
         <v>63828</v>
       </c>
-      <c r="E362" s="2" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -8209,7 +7826,6 @@
       <c r="D363" s="3" t="n">
         <v>53745</v>
       </c>
-      <c r="E363" s="2" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -8230,7 +7846,6 @@
       <c r="D364" s="3" t="n">
         <v>1205352</v>
       </c>
-      <c r="E364" s="2" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -8251,7 +7866,6 @@
       <c r="D365" s="3" t="n">
         <v>959291</v>
       </c>
-      <c r="E365" s="2" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -8272,7 +7886,6 @@
       <c r="D366" s="3" t="n">
         <v>959291</v>
       </c>
-      <c r="E366" s="2" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -8293,7 +7906,6 @@
       <c r="D367" s="3" t="n">
         <v>556957</v>
       </c>
-      <c r="E367" s="2" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" s="2" t="inlineStr">
@@ -8314,7 +7926,6 @@
       <c r="D368" s="3" t="n">
         <v>433922</v>
       </c>
-      <c r="E368" s="2" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
@@ -8335,7 +7946,6 @@
       <c r="D369" s="3" t="n">
         <v>433922</v>
       </c>
-      <c r="E369" s="2" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
@@ -8356,7 +7966,6 @@
       <c r="D370" s="3" t="n">
         <v>562699</v>
       </c>
-      <c r="E370" s="2" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
@@ -8377,7 +7986,6 @@
       <c r="D371" s="3" t="n">
         <v>438395</v>
       </c>
-      <c r="E371" s="2" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -8398,7 +8006,6 @@
       <c r="D372" s="3" t="n">
         <v>438395</v>
       </c>
-      <c r="E372" s="2" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -8419,7 +8026,6 @@
       <c r="D373" s="3" t="n">
         <v>379604</v>
       </c>
-      <c r="E373" s="2" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -8440,7 +8046,6 @@
       <c r="D374" s="3" t="n">
         <v>73230</v>
       </c>
-      <c r="E374" s="2" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
@@ -8461,7 +8066,6 @@
       <c r="D375" s="3" t="n">
         <v>509787</v>
       </c>
-      <c r="E375" s="2" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
@@ -8482,7 +8086,6 @@
       <c r="D376" s="3" t="n">
         <v>554292</v>
       </c>
-      <c r="E376" s="2" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
@@ -8503,7 +8106,6 @@
       <c r="D377" s="3" t="n">
         <v>181486</v>
       </c>
-      <c r="E377" s="2" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
@@ -8524,7 +8126,6 @@
       <c r="D378" s="3" t="n">
         <v>509787</v>
       </c>
-      <c r="E378" s="2" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" s="2" t="inlineStr">
@@ -8545,7 +8146,6 @@
       <c r="D379" s="3" t="n">
         <v>1306769</v>
       </c>
-      <c r="E379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -8566,7 +8166,6 @@
       <c r="D380" s="3" t="n">
         <v>554292</v>
       </c>
-      <c r="E380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -8587,7 +8186,6 @@
       <c r="D381" s="3" t="n">
         <v>67498</v>
       </c>
-      <c r="E381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -8608,7 +8206,6 @@
       <c r="D382" s="3" t="n">
         <v>50704</v>
       </c>
-      <c r="E382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -8629,7 +8226,6 @@
       <c r="D383" s="3" t="n">
         <v>50704</v>
       </c>
-      <c r="E383" s="2" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" s="2" t="inlineStr">
@@ -8650,7 +8246,6 @@
       <c r="D384" s="3" t="n">
         <v>601842</v>
       </c>
-      <c r="E384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -8671,7 +8266,6 @@
       <c r="D385" s="3" t="n">
         <v>601842</v>
       </c>
-      <c r="E385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -8692,7 +8286,6 @@
       <c r="D386" s="3" t="n">
         <v>255000</v>
       </c>
-      <c r="E386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -8713,7 +8306,6 @@
       <c r="D387" s="3" t="n">
         <v>328515</v>
       </c>
-      <c r="E387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -8734,7 +8326,6 @@
       <c r="D388" s="3" t="n">
         <v>402029</v>
       </c>
-      <c r="E388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -8755,7 +8346,6 @@
       <c r="D389" s="3" t="n">
         <v>475552</v>
       </c>
-      <c r="E389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -8776,7 +8366,6 @@
       <c r="D390" s="3" t="n">
         <v>549067</v>
       </c>
-      <c r="E390" s="2" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="2" t="inlineStr">
@@ -8797,7 +8386,6 @@
       <c r="D391" s="3" t="n">
         <v>623343</v>
       </c>
-      <c r="E391" s="2" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="2" t="inlineStr">
@@ -8818,7 +8406,6 @@
       <c r="D392" s="3" t="n">
         <v>696857</v>
       </c>
-      <c r="E392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -8839,7 +8426,6 @@
       <c r="D393" s="3" t="n">
         <v>770372</v>
       </c>
-      <c r="E393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -8860,7 +8446,6 @@
       <c r="D394" s="3" t="n">
         <v>843895</v>
       </c>
-      <c r="E394" s="2" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
@@ -8881,7 +8466,6 @@
       <c r="D395" s="3" t="n">
         <v>208286</v>
       </c>
-      <c r="E395" s="2" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
@@ -8902,7 +8486,6 @@
       <c r="D396" s="3" t="n">
         <v>288695</v>
       </c>
-      <c r="E396" s="2" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="2" t="inlineStr">
@@ -8923,7 +8506,6 @@
       <c r="D397" s="3" t="n">
         <v>369105</v>
       </c>
-      <c r="E397" s="2" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="2" t="inlineStr">
@@ -8944,7 +8526,6 @@
       <c r="D398" s="3" t="n">
         <v>449514</v>
       </c>
-      <c r="E398" s="2" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="2" t="inlineStr">
@@ -8965,7 +8546,6 @@
       <c r="D399" s="3" t="n">
         <v>530686</v>
       </c>
-      <c r="E399" s="2" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="2" t="inlineStr">
@@ -8986,7 +8566,6 @@
       <c r="D400" s="3" t="n">
         <v>611095</v>
       </c>
-      <c r="E400" s="2" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" s="2" t="inlineStr">
@@ -9007,7 +8586,6 @@
       <c r="D401" s="3" t="n">
         <v>186848</v>
       </c>
-      <c r="E401" s="2" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -9028,7 +8606,6 @@
       <c r="D402" s="3" t="n">
         <v>264953</v>
       </c>
-      <c r="E402" s="2" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -9049,7 +8626,6 @@
       <c r="D403" s="3" t="n">
         <v>343067</v>
       </c>
-      <c r="E403" s="2" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -9070,7 +8646,6 @@
       <c r="D404" s="3" t="n">
         <v>420410</v>
       </c>
-      <c r="E404" s="2" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" s="2" t="inlineStr">
@@ -9091,7 +8666,6 @@
       <c r="D405" s="3" t="n">
         <v>498524</v>
       </c>
-      <c r="E405" s="2" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" s="2" t="inlineStr">
@@ -9112,7 +8686,6 @@
       <c r="D406" s="3" t="n">
         <v>575867</v>
       </c>
-      <c r="E406" s="2" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" s="2" t="inlineStr">
@@ -9133,7 +8706,6 @@
       <c r="D407" s="3" t="n">
         <v>653972</v>
       </c>
-      <c r="E407" s="2" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" s="2" t="inlineStr">
@@ -9154,7 +8726,6 @@
       <c r="D408" s="3" t="n">
         <v>731324</v>
       </c>
-      <c r="E408" s="2" t="inlineStr"/>
     </row>
     <row r="409">
       <c r="A409" s="2" t="inlineStr">
@@ -9175,7 +8746,6 @@
       <c r="D409" s="3" t="n">
         <v>808667</v>
       </c>
-      <c r="E409" s="2" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
@@ -9196,7 +8766,6 @@
       <c r="D410" s="3" t="n">
         <v>886772</v>
       </c>
-      <c r="E410" s="2" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
@@ -9217,7 +8786,6 @@
       <c r="D411" s="3" t="n">
         <v>214419</v>
       </c>
-      <c r="E411" s="2" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
@@ -9238,7 +8806,6 @@
       <c r="D412" s="3" t="n">
         <v>299419</v>
       </c>
-      <c r="E412" s="2" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
@@ -9259,7 +8826,6 @@
       <c r="D413" s="3" t="n">
         <v>383648</v>
       </c>
-      <c r="E413" s="2" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
@@ -9280,7 +8846,6 @@
       <c r="D414" s="3" t="n">
         <v>20783</v>
       </c>
-      <c r="E414" s="2" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
@@ -9301,7 +8866,6 @@
       <c r="D415" s="3" t="n">
         <v>26220</v>
       </c>
-      <c r="E415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -9322,7 +8886,6 @@
       <c r="D416" s="3" t="n">
         <v>44175</v>
       </c>
-      <c r="E416" s="2" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
@@ -9343,7 +8906,6 @@
       <c r="D417" s="3" t="n">
         <v>43070</v>
       </c>
-      <c r="E417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -9364,7 +8926,6 @@
       <c r="D418" s="3" t="n">
         <v>72756</v>
       </c>
-      <c r="E418" s="2" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
@@ -9385,7 +8946,6 @@
       <c r="D419" s="3" t="n">
         <v>332618</v>
       </c>
-      <c r="E419" s="2" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
@@ -9406,7 +8966,6 @@
       <c r="D420" s="3" t="n">
         <v>46820</v>
       </c>
-      <c r="E420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -9427,7 +8986,6 @@
       <c r="D421" s="3" t="n">
         <v>46774</v>
       </c>
-      <c r="E421" s="2" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="2" t="inlineStr">
@@ -9448,7 +9006,6 @@
       <c r="D422" s="3" t="n">
         <v>83152</v>
       </c>
-      <c r="E422" s="2" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="2" t="inlineStr">
@@ -9469,7 +9026,6 @@
       <c r="D423" s="3" t="n">
         <v>62359</v>
       </c>
-      <c r="E423" s="2" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="2" t="inlineStr">
@@ -9490,7 +9046,6 @@
       <c r="D424" s="3" t="n">
         <v>62359</v>
       </c>
-      <c r="E424" s="2" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" s="2" t="inlineStr">
@@ -9511,7 +9066,6 @@
       <c r="D425" s="3" t="n">
         <v>102206</v>
       </c>
-      <c r="E425" s="2" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
@@ -9532,7 +9086,6 @@
       <c r="D426" s="3" t="n">
         <v>102206</v>
       </c>
-      <c r="E426" s="2" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
@@ -9553,7 +9106,6 @@
       <c r="D427" s="3" t="n">
         <v>291948</v>
       </c>
-      <c r="E427" s="2" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
@@ -9574,7 +9126,6 @@
       <c r="D428" s="3" t="n">
         <v>16333</v>
       </c>
-      <c r="E428" s="2" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
@@ -9595,7 +9146,6 @@
       <c r="D429" s="3" t="n">
         <v>11432</v>
       </c>
-      <c r="E429" s="2" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
@@ -9616,7 +9166,6 @@
       <c r="D430" s="3" t="n">
         <v>36385</v>
       </c>
-      <c r="E430" s="2" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
@@ -9637,7 +9186,6 @@
       <c r="D431" s="3" t="n">
         <v>5836</v>
       </c>
-      <c r="E431" s="2" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="2" t="inlineStr">
@@ -9658,7 +9206,6 @@
       <c r="D432" s="3" t="n">
         <v>6465</v>
       </c>
-      <c r="E432" s="2" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -9679,7 +9226,6 @@
       <c r="D433" s="3" t="n">
         <v>67919</v>
       </c>
-      <c r="E433" s="2" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="2" t="inlineStr">
@@ -9700,7 +9246,6 @@
       <c r="D434" s="3" t="n">
         <v>1519807</v>
       </c>
-      <c r="E434" s="2" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
@@ -9721,7 +9266,6 @@
       <c r="D435" s="3" t="n">
         <v>65893</v>
       </c>
-      <c r="E435" s="2" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
@@ -9742,7 +9286,6 @@
       <c r="D436" s="3" t="n">
         <v>250243</v>
       </c>
-      <c r="E436" s="2" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="2" t="inlineStr">
@@ -9763,7 +9306,6 @@
       <c r="D437" s="3" t="n">
         <v>2497</v>
       </c>
-      <c r="E437" s="2" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="2" t="inlineStr">
@@ -9784,7 +9326,6 @@
       <c r="D438" s="3" t="n">
         <v>5004</v>
       </c>
-      <c r="E438" s="2" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="inlineStr">
@@ -9805,7 +9346,6 @@
       <c r="D439" s="3" t="n">
         <v>8334</v>
       </c>
-      <c r="E439" s="2" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
@@ -9826,7 +9366,6 @@
       <c r="D440" s="3" t="n">
         <v>15012</v>
       </c>
-      <c r="E440" s="2" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
@@ -9847,7 +9386,6 @@
       <c r="D441" s="3" t="n">
         <v>583</v>
       </c>
-      <c r="E441" s="2" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
@@ -9868,7 +9406,6 @@
       <c r="D442" s="3" t="n">
         <v>7187030</v>
       </c>
-      <c r="E442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -9889,7 +9426,6 @@
       <c r="D443" s="3" t="n">
         <v>8738110</v>
       </c>
-      <c r="E443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -9910,7 +9446,6 @@
       <c r="D444" s="3" t="n">
         <v>13804820</v>
       </c>
-      <c r="E444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -9931,7 +9466,6 @@
       <c r="D445" s="3" t="n">
         <v>17633830</v>
       </c>
-      <c r="E445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -9952,7 +9486,6 @@
       <c r="D446" s="3" t="n">
         <v>2701838</v>
       </c>
-      <c r="E446" s="2" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" s="2" t="inlineStr">
@@ -9973,7 +9506,6 @@
       <c r="D447" s="3" t="n">
         <v>215612</v>
       </c>
-      <c r="E447" s="2" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="2" t="inlineStr">
@@ -9994,7 +9526,6 @@
       <c r="D448" s="3" t="n">
         <v>56783</v>
       </c>
-      <c r="E448" s="2" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" s="2" t="inlineStr">
@@ -10015,7 +9546,6 @@
       <c r="D449" s="3" t="n">
         <v>264415</v>
       </c>
-      <c r="E449" s="2" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="2" t="inlineStr">
@@ -10036,7 +9566,6 @@
       <c r="D450" s="3" t="n">
         <v>7489396</v>
       </c>
-      <c r="E450" s="2" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="2" t="inlineStr">
@@ -10057,7 +9586,6 @@
       <c r="D451" s="3" t="n">
         <v>1794121</v>
       </c>
-      <c r="E451" s="2" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="2" t="inlineStr">
@@ -10078,7 +9606,6 @@
       <c r="D452" s="3" t="n">
         <v>1794121</v>
       </c>
-      <c r="E452" s="2" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="2" t="inlineStr">
@@ -10099,7 +9626,6 @@
       <c r="D453" s="3" t="n">
         <v>755703</v>
       </c>
-      <c r="E453" s="2" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="2" t="inlineStr">
@@ -10120,7 +9646,6 @@
       <c r="D454" s="3" t="n">
         <v>768249</v>
       </c>
-      <c r="E454" s="2" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="2" t="inlineStr">
@@ -10141,7 +9666,6 @@
       <c r="D455" s="3" t="n">
         <v>75296</v>
       </c>
-      <c r="E455" s="2" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" s="2" t="inlineStr">
@@ -10162,7 +9686,6 @@
       <c r="D456" s="3" t="n">
         <v>29577</v>
       </c>
-      <c r="E456" s="2" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="2" t="inlineStr">
@@ -10183,7 +9706,6 @@
       <c r="D457" s="3" t="n">
         <v>260863</v>
       </c>
-      <c r="E457" s="2" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" s="2" t="inlineStr">
@@ -10204,7 +9726,6 @@
       <c r="D458" s="3" t="n">
         <v>645441</v>
       </c>
-      <c r="E458" s="2" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" s="2" t="inlineStr">
@@ -10225,7 +9746,6 @@
       <c r="D459" s="3" t="n">
         <v>735086</v>
       </c>
-      <c r="E459" s="2" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="2" t="inlineStr">
@@ -10246,7 +9766,6 @@
       <c r="D460" s="3" t="n">
         <v>641518</v>
       </c>
-      <c r="E460" s="2" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="2" t="inlineStr">
@@ -10267,7 +9786,6 @@
       <c r="D461" s="3" t="n">
         <v>645441</v>
       </c>
-      <c r="E461" s="2" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="2" t="inlineStr">
@@ -10288,7 +9806,6 @@
       <c r="D462" s="3" t="n">
         <v>645441</v>
       </c>
-      <c r="E462" s="2" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" s="2" t="inlineStr">
@@ -10309,7 +9826,6 @@
       <c r="D463" s="3" t="n">
         <v>735086</v>
       </c>
-      <c r="E463" s="2" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" s="2" t="inlineStr">
@@ -10330,7 +9846,6 @@
       <c r="D464" s="3" t="n">
         <v>641518</v>
       </c>
-      <c r="E464" s="2" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="inlineStr">
@@ -10351,7 +9866,6 @@
       <c r="D465" s="3" t="n">
         <v>735086</v>
       </c>
-      <c r="E465" s="2" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="2" t="inlineStr">
@@ -10372,7 +9886,6 @@
       <c r="D466" s="3" t="n">
         <v>641518</v>
       </c>
-      <c r="E466" s="2" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" s="2" t="inlineStr">
@@ -10393,7 +9906,6 @@
       <c r="D467" s="3" t="n">
         <v>1870424</v>
       </c>
-      <c r="E467" s="2" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="2" t="inlineStr">
@@ -10414,7 +9926,6 @@
       <c r="D468" s="3" t="n">
         <v>1870424</v>
       </c>
-      <c r="E468" s="2" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="2" t="inlineStr">
@@ -10435,7 +9946,6 @@
       <c r="D469" s="3" t="n">
         <v>290449</v>
       </c>
-      <c r="E469" s="2" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" s="2" t="inlineStr">
@@ -10456,7 +9966,6 @@
       <c r="D470" s="3" t="n">
         <v>88748</v>
       </c>
-      <c r="E470" s="2" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="2" t="inlineStr">
@@ -10477,7 +9986,6 @@
       <c r="D471" s="3" t="n">
         <v>37648</v>
       </c>
-      <c r="E471" s="2" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="2" t="inlineStr">
@@ -10498,7 +10006,6 @@
       <c r="D472" s="3" t="n">
         <v>645441</v>
       </c>
-      <c r="E472" s="2" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="2" t="inlineStr">
@@ -10519,7 +10026,6 @@
       <c r="D473" s="3" t="n">
         <v>735086</v>
       </c>
-      <c r="E473" s="2" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="2" t="inlineStr">
@@ -10540,7 +10046,6 @@
       <c r="D474" s="3" t="n">
         <v>641518</v>
       </c>
-      <c r="E474" s="2" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="2" t="inlineStr">
@@ -10561,7 +10066,6 @@
       <c r="D475" s="3" t="n">
         <v>137298</v>
       </c>
-      <c r="E475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="4" t="inlineStr">
@@ -10582,7 +10086,6 @@
       <c r="D476" s="3" t="n">
         <v>7911208</v>
       </c>
-      <c r="E476" s="2" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="4" t="inlineStr">
@@ -10603,7 +10106,6 @@
       <c r="D477" s="3" t="n">
         <v>2984898</v>
       </c>
-      <c r="E477" s="2" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="4" t="inlineStr">
@@ -10624,7 +10126,6 @@
       <c r="D478" s="3" t="n">
         <v>5211108</v>
       </c>
-      <c r="E478" s="2" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="4" t="inlineStr">
@@ -10645,7 +10146,6 @@
       <c r="D479" s="3" t="n">
         <v>3301512</v>
       </c>
-      <c r="E479" s="2" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="4" t="inlineStr">
@@ -10666,7 +10166,6 @@
       <c r="D480" s="3" t="n">
         <v>2176663</v>
       </c>
-      <c r="E480" s="2" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" s="4" t="inlineStr">
@@ -10687,7 +10186,6 @@
       <c r="D481" s="3" t="n">
         <v>2112641</v>
       </c>
-      <c r="E481" s="2" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="4" t="inlineStr">
@@ -10708,7 +10206,6 @@
       <c r="D482" s="3" t="n">
         <v>212401</v>
       </c>
-      <c r="E482" s="2" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="4" t="inlineStr">
@@ -10729,7 +10226,6 @@
       <c r="D483" s="3" t="n">
         <v>311102</v>
       </c>
-      <c r="E483" s="2" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" s="4" t="inlineStr">
@@ -10750,7 +10246,6 @@
       <c r="D484" s="3" t="n">
         <v>7491044</v>
       </c>
-      <c r="E484" s="2" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="4" t="inlineStr">
@@ -10771,7 +10266,6 @@
       <c r="D485" s="3" t="n">
         <v>4588310</v>
       </c>
-      <c r="E485" s="2" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="4" t="inlineStr">
@@ -10792,7 +10286,6 @@
       <c r="D486" s="3" t="n">
         <v>4863056</v>
       </c>
-      <c r="E486" s="2" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="4" t="inlineStr">
@@ -10813,7 +10306,6 @@
       <c r="D487" s="3" t="n">
         <v>3550012</v>
       </c>
-      <c r="E487" s="2" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="4" t="inlineStr">
@@ -10831,13 +10323,8 @@
           <t>CER_8GHz_11GHz_6+0_SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D488" s="5" t="n">
+      <c r="D488" s="3" t="n">
         <v>1826945</v>
-      </c>
-      <c r="E488" s="4" t="inlineStr">
-        <is>
-          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
-        </is>
       </c>
     </row>
     <row r="489">
@@ -10856,13 +10343,8 @@
           <t>CER_8GHz_11GHz_6+0_Non SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D489" s="5" t="n">
+      <c r="D489" s="3" t="n">
         <v>2449121</v>
-      </c>
-      <c r="E489" s="4" t="inlineStr">
-        <is>
-          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
-        </is>
       </c>
     </row>
     <row r="490">
@@ -10881,13 +10363,8 @@
           <t>CER_8GHz_11GHz_8+0_SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D490" s="5" t="n">
+      <c r="D490" s="3" t="n">
         <v>326933</v>
-      </c>
-      <c r="E490" s="4" t="inlineStr">
-        <is>
-          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
-        </is>
       </c>
     </row>
     <row r="491">
@@ -10906,13 +10383,8 @@
           <t>CER_8GHz_11GHz_8+0_Non SD_Configuration SW Package</t>
         </is>
       </c>
-      <c r="D491" s="5" t="n">
+      <c r="D491" s="3" t="n">
         <v>901776</v>
-      </c>
-      <c r="E491" s="4" t="inlineStr">
-        <is>
-          <t>SD가 Non_SD보다 싼 역전 현상 확인 중(대성 회신 대기, 18번 파일 참고)</t>
-        </is>
       </c>
     </row>
     <row r="492">
@@ -10934,7 +10406,6 @@
       <c r="D492" s="3" t="n">
         <v>9524845</v>
       </c>
-      <c r="E492" s="2" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="4" t="inlineStr">
@@ -10955,7 +10426,6 @@
       <c r="D493" s="3" t="n">
         <v>312186</v>
       </c>
-      <c r="E493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="4" t="inlineStr">
@@ -10976,10 +10446,9 @@
       <c r="D494" s="3" t="n">
         <v>312186</v>
       </c>
-      <c r="E494" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E494"/>
+  <autoFilter ref="A1:D494"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>